--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="86">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -218,12 +218,69 @@
   </si>
   <si>
     <t>Nº</t>
+  </si>
+  <si>
+    <t>Switzerland Super League</t>
+  </si>
+  <si>
+    <t>2025/2026</t>
+  </si>
+  <si>
+    <t>Zürich</t>
+  </si>
+  <si>
+    <t>St. Gallen</t>
+  </si>
+  <si>
+    <t>Grasshopper</t>
+  </si>
+  <si>
+    <t>Young Boys</t>
+  </si>
+  <si>
+    <t>Sion</t>
+  </si>
+  <si>
+    <t>Basel</t>
+  </si>
+  <si>
+    <t>Luzern</t>
+  </si>
+  <si>
+    <t>Servette</t>
+  </si>
+  <si>
+    <t>['27', '55']</t>
+  </si>
+  <si>
+    <t>['56', '75']</t>
+  </si>
+  <si>
+    <t>['5', '31']</t>
+  </si>
+  <si>
+    <t>['84', '14', '10']</t>
+  </si>
+  <si>
+    <t>['81', '90+1', '87']</t>
+  </si>
+  <si>
+    <t>['40']</t>
+  </si>
+  <si>
+    <t>['38', '16', '69']</t>
+  </si>
+  <si>
+    <t>['36']</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -276,11 +333,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -575,7 +633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP1"/>
+  <dimension ref="A1:BP5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -784,6 +842,830 @@
         <v>66</v>
       </c>
     </row>
+    <row r="2" spans="1:68">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>7962647</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="2">
+        <v>45863.64583333334</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>3</v>
+      </c>
+      <c r="N2">
+        <v>5</v>
+      </c>
+      <c r="O2" t="s">
+        <v>78</v>
+      </c>
+      <c r="P2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q2">
+        <v>2.53</v>
+      </c>
+      <c r="R2">
+        <v>2.15</v>
+      </c>
+      <c r="S2">
+        <v>3.7</v>
+      </c>
+      <c r="T2">
+        <v>1.3</v>
+      </c>
+      <c r="U2">
+        <v>3.25</v>
+      </c>
+      <c r="V2">
+        <v>2.67</v>
+      </c>
+      <c r="W2">
+        <v>1.51</v>
+      </c>
+      <c r="X2">
+        <v>5.65</v>
+      </c>
+      <c r="Y2">
+        <v>1.1</v>
+      </c>
+      <c r="Z2">
+        <v>2.05</v>
+      </c>
+      <c r="AA2">
+        <v>3.4</v>
+      </c>
+      <c r="AB2">
+        <v>3.3</v>
+      </c>
+      <c r="AC2">
+        <v>1.02</v>
+      </c>
+      <c r="AD2">
+        <v>12.9</v>
+      </c>
+      <c r="AE2">
+        <v>1.22</v>
+      </c>
+      <c r="AF2">
+        <v>3.9</v>
+      </c>
+      <c r="AG2">
+        <v>1.78</v>
+      </c>
+      <c r="AH2">
+        <v>1.98</v>
+      </c>
+      <c r="AI2">
+        <v>1.66</v>
+      </c>
+      <c r="AJ2">
+        <v>2.13</v>
+      </c>
+      <c r="AK2">
+        <v>1.32</v>
+      </c>
+      <c r="AL2">
+        <v>1.22</v>
+      </c>
+      <c r="AM2">
+        <v>1.81</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <v>3</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>6</v>
+      </c>
+      <c r="AV2">
+        <v>7</v>
+      </c>
+      <c r="AW2">
+        <v>4</v>
+      </c>
+      <c r="AX2">
+        <v>9</v>
+      </c>
+      <c r="AY2">
+        <v>10</v>
+      </c>
+      <c r="AZ2">
+        <v>16</v>
+      </c>
+      <c r="BA2">
+        <v>3</v>
+      </c>
+      <c r="BB2">
+        <v>2</v>
+      </c>
+      <c r="BC2">
+        <v>5</v>
+      </c>
+      <c r="BD2">
+        <v>1.47</v>
+      </c>
+      <c r="BE2">
+        <v>9.5</v>
+      </c>
+      <c r="BF2">
+        <v>3.2</v>
+      </c>
+      <c r="BG2">
+        <v>1.2</v>
+      </c>
+      <c r="BH2">
+        <v>4.2</v>
+      </c>
+      <c r="BI2">
+        <v>1.4</v>
+      </c>
+      <c r="BJ2">
+        <v>2.75</v>
+      </c>
+      <c r="BK2">
+        <v>1.53</v>
+      </c>
+      <c r="BL2">
+        <v>2.2</v>
+      </c>
+      <c r="BM2">
+        <v>1.9</v>
+      </c>
+      <c r="BN2">
+        <v>1.72</v>
+      </c>
+      <c r="BO2">
+        <v>2.55</v>
+      </c>
+      <c r="BP2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:68">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>7962648</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="2">
+        <v>45864.54166666666</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>3</v>
+      </c>
+      <c r="O3" t="s">
+        <v>79</v>
+      </c>
+      <c r="P3" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q3">
+        <v>3.82</v>
+      </c>
+      <c r="R3">
+        <v>2.48</v>
+      </c>
+      <c r="S3">
+        <v>2.15</v>
+      </c>
+      <c r="T3">
+        <v>1.25</v>
+      </c>
+      <c r="U3">
+        <v>3.8</v>
+      </c>
+      <c r="V3">
+        <v>2.15</v>
+      </c>
+      <c r="W3">
+        <v>1.66</v>
+      </c>
+      <c r="X3">
+        <v>4.6</v>
+      </c>
+      <c r="Y3">
+        <v>1.11</v>
+      </c>
+      <c r="Z3">
+        <v>4.4</v>
+      </c>
+      <c r="AA3">
+        <v>3.65</v>
+      </c>
+      <c r="AB3">
+        <v>2.01</v>
+      </c>
+      <c r="AC3">
+        <v>1</v>
+      </c>
+      <c r="AD3">
+        <v>11</v>
+      </c>
+      <c r="AE3">
+        <v>1.2</v>
+      </c>
+      <c r="AF3">
+        <v>4.3</v>
+      </c>
+      <c r="AG3">
+        <v>1.47</v>
+      </c>
+      <c r="AH3">
+        <v>2.45</v>
+      </c>
+      <c r="AI3">
+        <v>1.53</v>
+      </c>
+      <c r="AJ3">
+        <v>2.38</v>
+      </c>
+      <c r="AK3">
+        <v>1.25</v>
+      </c>
+      <c r="AL3">
+        <v>1.22</v>
+      </c>
+      <c r="AM3">
+        <v>1.2</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>3</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>9</v>
+      </c>
+      <c r="AV3">
+        <v>7</v>
+      </c>
+      <c r="AW3">
+        <v>9</v>
+      </c>
+      <c r="AX3">
+        <v>14</v>
+      </c>
+      <c r="AY3">
+        <v>18</v>
+      </c>
+      <c r="AZ3">
+        <v>21</v>
+      </c>
+      <c r="BA3">
+        <v>8</v>
+      </c>
+      <c r="BB3">
+        <v>5</v>
+      </c>
+      <c r="BC3">
+        <v>13</v>
+      </c>
+      <c r="BD3">
+        <v>2.25</v>
+      </c>
+      <c r="BE3">
+        <v>6.75</v>
+      </c>
+      <c r="BF3">
+        <v>1.93</v>
+      </c>
+      <c r="BG3">
+        <v>1.28</v>
+      </c>
+      <c r="BH3">
+        <v>4.45</v>
+      </c>
+      <c r="BI3">
+        <v>1.49</v>
+      </c>
+      <c r="BJ3">
+        <v>2.38</v>
+      </c>
+      <c r="BK3">
+        <v>1.6</v>
+      </c>
+      <c r="BL3">
+        <v>2.25</v>
+      </c>
+      <c r="BM3">
+        <v>1.95</v>
+      </c>
+      <c r="BN3">
+        <v>1.8</v>
+      </c>
+      <c r="BO3">
+        <v>2.88</v>
+      </c>
+      <c r="BP3">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:68">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>7962649</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="2">
+        <v>45864.54166666666</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>3</v>
+      </c>
+      <c r="N4">
+        <v>5</v>
+      </c>
+      <c r="O4" t="s">
+        <v>80</v>
+      </c>
+      <c r="P4" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q4">
+        <v>3.06</v>
+      </c>
+      <c r="R4">
+        <v>2</v>
+      </c>
+      <c r="S4">
+        <v>3.4</v>
+      </c>
+      <c r="T4">
+        <v>1.35</v>
+      </c>
+      <c r="U4">
+        <v>2.88</v>
+      </c>
+      <c r="V4">
+        <v>2.6</v>
+      </c>
+      <c r="W4">
+        <v>1.43</v>
+      </c>
+      <c r="X4">
+        <v>6.5</v>
+      </c>
+      <c r="Y4">
+        <v>1.1</v>
+      </c>
+      <c r="Z4">
+        <v>2.17</v>
+      </c>
+      <c r="AA4">
+        <v>3.45</v>
+      </c>
+      <c r="AB4">
+        <v>2.5</v>
+      </c>
+      <c r="AC4">
+        <v>1.05</v>
+      </c>
+      <c r="AD4">
+        <v>9.5</v>
+      </c>
+      <c r="AE4">
+        <v>1.26</v>
+      </c>
+      <c r="AF4">
+        <v>3.48</v>
+      </c>
+      <c r="AG4">
+        <v>1.86</v>
+      </c>
+      <c r="AH4">
+        <v>1.93</v>
+      </c>
+      <c r="AI4">
+        <v>1.66</v>
+      </c>
+      <c r="AJ4">
+        <v>2.1</v>
+      </c>
+      <c r="AK4">
+        <v>1.29</v>
+      </c>
+      <c r="AL4">
+        <v>1.25</v>
+      </c>
+      <c r="AM4">
+        <v>1.51</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>3</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>7</v>
+      </c>
+      <c r="AV4">
+        <v>6</v>
+      </c>
+      <c r="AW4">
+        <v>9</v>
+      </c>
+      <c r="AX4">
+        <v>6</v>
+      </c>
+      <c r="AY4">
+        <v>16</v>
+      </c>
+      <c r="AZ4">
+        <v>12</v>
+      </c>
+      <c r="BA4">
+        <v>9</v>
+      </c>
+      <c r="BB4">
+        <v>4</v>
+      </c>
+      <c r="BC4">
+        <v>13</v>
+      </c>
+      <c r="BD4">
+        <v>1.8</v>
+      </c>
+      <c r="BE4">
+        <v>8.5</v>
+      </c>
+      <c r="BF4">
+        <v>2.28</v>
+      </c>
+      <c r="BG4">
+        <v>1.21</v>
+      </c>
+      <c r="BH4">
+        <v>3.4</v>
+      </c>
+      <c r="BI4">
+        <v>1.45</v>
+      </c>
+      <c r="BJ4">
+        <v>2.6</v>
+      </c>
+      <c r="BK4">
+        <v>1.72</v>
+      </c>
+      <c r="BL4">
+        <v>2</v>
+      </c>
+      <c r="BM4">
+        <v>2.21</v>
+      </c>
+      <c r="BN4">
+        <v>1.56</v>
+      </c>
+      <c r="BO4">
+        <v>2.8</v>
+      </c>
+      <c r="BP4">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:68">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>7962650</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="2">
+        <v>45864.64583333334</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>4</v>
+      </c>
+      <c r="O5" t="s">
+        <v>81</v>
+      </c>
+      <c r="P5" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q5">
+        <v>2.42</v>
+      </c>
+      <c r="R5">
+        <v>2.34</v>
+      </c>
+      <c r="S5">
+        <v>3.8</v>
+      </c>
+      <c r="T5">
+        <v>1.27</v>
+      </c>
+      <c r="U5">
+        <v>3.4</v>
+      </c>
+      <c r="V5">
+        <v>2.3</v>
+      </c>
+      <c r="W5">
+        <v>1.55</v>
+      </c>
+      <c r="X5">
+        <v>5.5</v>
+      </c>
+      <c r="Y5">
+        <v>1.12</v>
+      </c>
+      <c r="Z5">
+        <v>2.03</v>
+      </c>
+      <c r="AA5">
+        <v>3.75</v>
+      </c>
+      <c r="AB5">
+        <v>3.25</v>
+      </c>
+      <c r="AC5">
+        <v>1.02</v>
+      </c>
+      <c r="AD5">
+        <v>10</v>
+      </c>
+      <c r="AE5">
+        <v>1.18</v>
+      </c>
+      <c r="AF5">
+        <v>4.35</v>
+      </c>
+      <c r="AG5">
+        <v>1.64</v>
+      </c>
+      <c r="AH5">
+        <v>2.23</v>
+      </c>
+      <c r="AI5">
+        <v>1.57</v>
+      </c>
+      <c r="AJ5">
+        <v>2.52</v>
+      </c>
+      <c r="AK5">
+        <v>1.3</v>
+      </c>
+      <c r="AL5">
+        <v>1.25</v>
+      </c>
+      <c r="AM5">
+        <v>1.83</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>3</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>5</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>17</v>
+      </c>
+      <c r="AX5">
+        <v>7</v>
+      </c>
+      <c r="AY5">
+        <v>22</v>
+      </c>
+      <c r="AZ5">
+        <v>7</v>
+      </c>
+      <c r="BA5">
+        <v>8</v>
+      </c>
+      <c r="BB5">
+        <v>2</v>
+      </c>
+      <c r="BC5">
+        <v>10</v>
+      </c>
+      <c r="BD5">
+        <v>1.51</v>
+      </c>
+      <c r="BE5">
+        <v>9.5</v>
+      </c>
+      <c r="BF5">
+        <v>3.5</v>
+      </c>
+      <c r="BG5">
+        <v>1.17</v>
+      </c>
+      <c r="BH5">
+        <v>4.5</v>
+      </c>
+      <c r="BI5">
+        <v>1.3</v>
+      </c>
+      <c r="BJ5">
+        <v>3.4</v>
+      </c>
+      <c r="BK5">
+        <v>1.44</v>
+      </c>
+      <c r="BL5">
+        <v>2.53</v>
+      </c>
+      <c r="BM5">
+        <v>1.66</v>
+      </c>
+      <c r="BN5">
+        <v>2.04</v>
+      </c>
+      <c r="BO5">
+        <v>2.22</v>
+      </c>
+      <c r="BP5">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="94">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -238,6 +238,12 @@
     <t>Young Boys</t>
   </si>
   <si>
+    <t>Lausanne Sport</t>
+  </si>
+  <si>
+    <t>Lugano</t>
+  </si>
+  <si>
     <t>Sion</t>
   </si>
   <si>
@@ -250,6 +256,12 @@
     <t>Servette</t>
   </si>
   <si>
+    <t>Winterthur</t>
+  </si>
+  <si>
+    <t>Thun</t>
+  </si>
+  <si>
     <t>['27', '55']</t>
   </si>
   <si>
@@ -259,19 +271,31 @@
     <t>['5', '31']</t>
   </si>
   <si>
-    <t>['84', '14', '10']</t>
-  </si>
-  <si>
-    <t>['81', '90+1', '87']</t>
+    <t>['10', '14', '84']</t>
+  </si>
+  <si>
+    <t>['61', '81', '90+3']</t>
+  </si>
+  <si>
+    <t>['16']</t>
+  </si>
+  <si>
+    <t>['81', '87', '90+1']</t>
   </si>
   <si>
     <t>['40']</t>
   </si>
   <si>
-    <t>['38', '16', '69']</t>
+    <t>['16', '38', '69']</t>
   </si>
   <si>
     <t>['36']</t>
+  </si>
+  <si>
+    <t>['43', '64']</t>
+  </si>
+  <si>
+    <t>['63', '85']</t>
   </si>
 </sst>
 </file>
@@ -633,7 +657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP5"/>
+  <dimension ref="A1:BP7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -865,7 +889,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -886,10 +910,10 @@
         <v>5</v>
       </c>
       <c r="O2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="Q2">
         <v>2.53</v>
@@ -1071,7 +1095,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1092,10 +1116,10 @@
         <v>3</v>
       </c>
       <c r="O3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="Q3">
         <v>3.82</v>
@@ -1277,7 +1301,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I4">
         <v>2</v>
@@ -1298,10 +1322,10 @@
         <v>5</v>
       </c>
       <c r="O4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="Q4">
         <v>3.06</v>
@@ -1483,7 +1507,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I5">
         <v>2</v>
@@ -1504,10 +1528,10 @@
         <v>4</v>
       </c>
       <c r="O5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="Q5">
         <v>2.42</v>
@@ -1664,6 +1688,418 @@
       </c>
       <c r="BP5">
         <v>1.61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:68">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>7962651</v>
+      </c>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="2">
+        <v>45865.45833333334</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+      <c r="N6">
+        <v>5</v>
+      </c>
+      <c r="O6" t="s">
+        <v>86</v>
+      </c>
+      <c r="P6" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q6">
+        <v>2.25</v>
+      </c>
+      <c r="R6">
+        <v>2.45</v>
+      </c>
+      <c r="S6">
+        <v>4.1</v>
+      </c>
+      <c r="T6">
+        <v>1.22</v>
+      </c>
+      <c r="U6">
+        <v>3.3</v>
+      </c>
+      <c r="V6">
+        <v>2.25</v>
+      </c>
+      <c r="W6">
+        <v>1.56</v>
+      </c>
+      <c r="X6">
+        <v>5.3</v>
+      </c>
+      <c r="Y6">
+        <v>1.13</v>
+      </c>
+      <c r="Z6">
+        <v>1.7</v>
+      </c>
+      <c r="AA6">
+        <v>3.83</v>
+      </c>
+      <c r="AB6">
+        <v>3.71</v>
+      </c>
+      <c r="AC6">
+        <v>1.03</v>
+      </c>
+      <c r="AD6">
+        <v>12</v>
+      </c>
+      <c r="AE6">
+        <v>1.16</v>
+      </c>
+      <c r="AF6">
+        <v>4.75</v>
+      </c>
+      <c r="AG6">
+        <v>1.61</v>
+      </c>
+      <c r="AH6">
+        <v>2.05</v>
+      </c>
+      <c r="AI6">
+        <v>1.55</v>
+      </c>
+      <c r="AJ6">
+        <v>2.28</v>
+      </c>
+      <c r="AK6">
+        <v>1.25</v>
+      </c>
+      <c r="AL6">
+        <v>1.2</v>
+      </c>
+      <c r="AM6">
+        <v>2</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>3</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>7</v>
+      </c>
+      <c r="AV6">
+        <v>3</v>
+      </c>
+      <c r="AW6">
+        <v>18</v>
+      </c>
+      <c r="AX6">
+        <v>5</v>
+      </c>
+      <c r="AY6">
+        <v>25</v>
+      </c>
+      <c r="AZ6">
+        <v>8</v>
+      </c>
+      <c r="BA6">
+        <v>12</v>
+      </c>
+      <c r="BB6">
+        <v>2</v>
+      </c>
+      <c r="BC6">
+        <v>14</v>
+      </c>
+      <c r="BD6">
+        <v>1.42</v>
+      </c>
+      <c r="BE6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF6">
+        <v>3.44</v>
+      </c>
+      <c r="BG6">
+        <v>1.19</v>
+      </c>
+      <c r="BH6">
+        <v>3.8</v>
+      </c>
+      <c r="BI6">
+        <v>1.29</v>
+      </c>
+      <c r="BJ6">
+        <v>2.65</v>
+      </c>
+      <c r="BK6">
+        <v>1.7</v>
+      </c>
+      <c r="BL6">
+        <v>2.19</v>
+      </c>
+      <c r="BM6">
+        <v>1.98</v>
+      </c>
+      <c r="BN6">
+        <v>1.73</v>
+      </c>
+      <c r="BO6">
+        <v>2.43</v>
+      </c>
+      <c r="BP6">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:68">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>7962652</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45865.45833333334</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
+      </c>
+      <c r="N7">
+        <v>3</v>
+      </c>
+      <c r="O7" t="s">
+        <v>87</v>
+      </c>
+      <c r="P7" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q7">
+        <v>2.3</v>
+      </c>
+      <c r="R7">
+        <v>2.43</v>
+      </c>
+      <c r="S7">
+        <v>4.1</v>
+      </c>
+      <c r="T7">
+        <v>1.31</v>
+      </c>
+      <c r="U7">
+        <v>3.4</v>
+      </c>
+      <c r="V7">
+        <v>2.32</v>
+      </c>
+      <c r="W7">
+        <v>1.5</v>
+      </c>
+      <c r="X7">
+        <v>5.5</v>
+      </c>
+      <c r="Y7">
+        <v>1.11</v>
+      </c>
+      <c r="Z7">
+        <v>1.56</v>
+      </c>
+      <c r="AA7">
+        <v>3.96</v>
+      </c>
+      <c r="AB7">
+        <v>4.4</v>
+      </c>
+      <c r="AC7">
+        <v>1.03</v>
+      </c>
+      <c r="AD7">
+        <v>12</v>
+      </c>
+      <c r="AE7">
+        <v>1.19</v>
+      </c>
+      <c r="AF7">
+        <v>4.4</v>
+      </c>
+      <c r="AG7">
+        <v>1.55</v>
+      </c>
+      <c r="AH7">
+        <v>2.2</v>
+      </c>
+      <c r="AI7">
+        <v>1.66</v>
+      </c>
+      <c r="AJ7">
+        <v>2.17</v>
+      </c>
+      <c r="AK7">
+        <v>1.28</v>
+      </c>
+      <c r="AL7">
+        <v>1.17</v>
+      </c>
+      <c r="AM7">
+        <v>2.13</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>3</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>8</v>
+      </c>
+      <c r="AV7">
+        <v>3</v>
+      </c>
+      <c r="AW7">
+        <v>4</v>
+      </c>
+      <c r="AX7">
+        <v>21</v>
+      </c>
+      <c r="AY7">
+        <v>12</v>
+      </c>
+      <c r="AZ7">
+        <v>24</v>
+      </c>
+      <c r="BA7">
+        <v>5</v>
+      </c>
+      <c r="BB7">
+        <v>1</v>
+      </c>
+      <c r="BC7">
+        <v>6</v>
+      </c>
+      <c r="BD7">
+        <v>1.49</v>
+      </c>
+      <c r="BE7">
+        <v>7.5</v>
+      </c>
+      <c r="BF7">
+        <v>2.95</v>
+      </c>
+      <c r="BG7">
+        <v>1.34</v>
+      </c>
+      <c r="BH7">
+        <v>3.1</v>
+      </c>
+      <c r="BI7">
+        <v>1.55</v>
+      </c>
+      <c r="BJ7">
+        <v>2.3</v>
+      </c>
+      <c r="BK7">
+        <v>1.9</v>
+      </c>
+      <c r="BL7">
+        <v>1.8</v>
+      </c>
+      <c r="BM7">
+        <v>2.4</v>
+      </c>
+      <c r="BN7">
+        <v>1.5</v>
+      </c>
+      <c r="BO7">
+        <v>3.2</v>
+      </c>
+      <c r="BP7">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP7"/>
+  <dimension ref="A1:BP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -926,10 +926,10 @@
         <v>0</v>
       </c>
       <c r="AU2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV2" t="n">
         <v>6</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>7</v>
       </c>
       <c r="AW2" t="n">
         <v>4</v>
@@ -938,10 +938,10 @@
         <v>9</v>
       </c>
       <c r="AY2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA2" t="n">
         <v>3</v>
@@ -1144,10 +1144,10 @@
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW3" t="n">
         <v>9</v>
@@ -1156,10 +1156,10 @@
         <v>14</v>
       </c>
       <c r="AY3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA3" t="n">
         <v>8</v>
@@ -1362,10 +1362,10 @@
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW4" t="n">
         <v>9</v>
@@ -1374,10 +1374,10 @@
         <v>6</v>
       </c>
       <c r="AY4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA4" t="n">
         <v>9</v>
@@ -1580,7 +1580,7 @@
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -1589,13 +1589,13 @@
         <v>17</v>
       </c>
       <c r="AX5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA5" t="n">
         <v>8</v>
@@ -1798,10 +1798,10 @@
         <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW6" t="n">
         <v>18</v>
@@ -1810,10 +1810,10 @@
         <v>5</v>
       </c>
       <c r="AY6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA6" t="n">
         <v>12</v>
@@ -2016,10 +2016,10 @@
         <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW7" t="n">
         <v>4</v>
@@ -2028,10 +2028,10 @@
         <v>21</v>
       </c>
       <c r="AY7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA7" t="n">
         <v>5</v>
@@ -2080,6 +2080,660 @@
       </c>
       <c r="BP7" t="n">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>7962653</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>45871.54166666666</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Winterthur</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Young Boys</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>['64']</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>['24']</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>7962654</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>45871.54166666666</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Servette</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>St. Gallen</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>['27']</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>['11', '18', '30', '90+6']</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V9" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>7962655</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>45871.64583333334</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Basel</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>['45', '75']</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>['69']</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="S10" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="V10" t="n">
+        <v>2</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="X10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP10"/>
+  <dimension ref="A1:BP12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2234,22 +2234,22 @@
         <v>0</v>
       </c>
       <c r="AU8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV8" t="n">
         <v>5</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AW8" t="n">
         <v>6</v>
       </c>
-      <c r="AW8" t="n">
-        <v>10</v>
-      </c>
       <c r="AX8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>11</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>17</v>
       </c>
       <c r="BA8" t="n">
         <v>3</v>
@@ -2452,22 +2452,22 @@
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY9" t="n">
         <v>10</v>
       </c>
-      <c r="AX9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>14</v>
-      </c>
       <c r="AZ9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA9" t="n">
         <v>1</v>
@@ -2734,6 +2734,442 @@
       </c>
       <c r="BP10" t="n">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>7962656</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>45872.375</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Thun</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Lausanne Sport</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>['10', '47']</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>['71']</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X11" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>7962657</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>45872.47916666666</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Luzern</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Zürich</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>['72']</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>['78']</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1.53</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -2234,22 +2234,22 @@
         <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AX8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AY8" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AZ8" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="BA8" t="n">
         <v>3</v>
@@ -2452,22 +2452,22 @@
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AX9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY9" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AZ9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BA9" t="n">
         <v>1</v>
@@ -3106,22 +3106,22 @@
         <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV12" t="n">
         <v>2</v>
       </c>
       <c r="AW12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AX12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA12" t="n">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP14"/>
+  <dimension ref="A1:BP16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AQ12" t="n">
         <v>1</v>
@@ -3606,6 +3606,442 @@
       </c>
       <c r="BP14" t="n">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>7962664</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>45878.54166666666</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>St. Gallen</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Winterthur</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>5</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>['7', '27', '45+5', '68', '77']</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>7962665</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>45878.64583333334</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Luzern</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Thun</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>['13']</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>['39', '46']</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -3760,22 +3760,22 @@
         <v>2.7</v>
       </c>
       <c r="AU15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW15" t="n">
         <v>8</v>
       </c>
       <c r="AX15" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AY15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ15" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="BA15" t="n">
         <v>3</v>
@@ -3984,16 +3984,16 @@
         <v>4</v>
       </c>
       <c r="AW16" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AX16" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AY16" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AZ16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BA16" t="n">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP16"/>
+  <dimension ref="A1:BP20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ5" t="n">
         <v>0</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>3</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AQ9" t="n">
         <v>3</v>
@@ -2658,7 +2658,7 @@
         <v>3</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -4042,6 +4042,878 @@
       </c>
       <c r="BP16" t="n">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="n">
+        <v>7962666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>45879.375</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Young Boys</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sion</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X17" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>7962668</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>45879.47916666666</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lugano</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Basel</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>['11', '31', '90+6']</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>['63']</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>7962667</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>45879.47916666666</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lausanne Sport</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Zürich</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>['41']</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>['24', '66']</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X19" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>8125649</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>45879.47916666666</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Servette</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>['74']</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>['33']</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X20" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -2037,10 +2037,10 @@
         <v>5</v>
       </c>
       <c r="BB7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD7" t="n">
         <v>1.49</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP20"/>
+  <dimension ref="A1:BP21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4914,6 +4914,224 @@
       </c>
       <c r="BP20" t="n">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>7962660</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>45892.54166666666</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Zürich</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Thun</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>4</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>['14', '41', '59', '90+2']</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="V21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X21" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -5086,13 +5086,13 @@
         <v>10</v>
       </c>
       <c r="BA21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB21" t="n">
         <v>3</v>
       </c>
       <c r="BC21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD21" t="n">
         <v>1.92</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -1147,16 +1147,16 @@
         <v>8</v>
       </c>
       <c r="AV3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AX3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AZ3" t="n">
         <v>20</v>
@@ -1362,13 +1362,13 @@
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV4" t="n">
         <v>5</v>
       </c>
       <c r="AW4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX4" t="n">
         <v>6</v>
@@ -1583,19 +1583,19 @@
         <v>4</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AX5" t="n">
         <v>6</v>
       </c>
       <c r="AY5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA5" t="n">
         <v>8</v>
@@ -1804,16 +1804,16 @@
         <v>2</v>
       </c>
       <c r="AW6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA6" t="n">
         <v>12</v>
@@ -2016,7 +2016,7 @@
         <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV7" t="n">
         <v>2</v>
@@ -2025,13 +2025,13 @@
         <v>4</v>
       </c>
       <c r="AX7" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AY7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BA7" t="n">
         <v>5</v>
@@ -2234,19 +2234,19 @@
         <v>0</v>
       </c>
       <c r="AU8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV8" t="n">
         <v>5</v>
       </c>
-      <c r="AV8" t="n">
-        <v>6</v>
-      </c>
       <c r="AW8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AX8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY8" t="n">
         <v>11</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>15</v>
       </c>
       <c r="AZ8" t="n">
         <v>17</v>
@@ -2452,22 +2452,22 @@
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY9" t="n">
         <v>14</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA9" t="n">
         <v>1</v>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>['45', '75']</t>
+          <t>['44', '75']</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -2894,13 +2894,13 @@
         <v>5</v>
       </c>
       <c r="AW11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX11" t="n">
         <v>8</v>
       </c>
       <c r="AY11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ11" t="n">
         <v>13</v>
@@ -3106,7 +3106,7 @@
         <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV12" t="n">
         <v>2</v>
@@ -3118,7 +3118,7 @@
         <v>3</v>
       </c>
       <c r="AY12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ12" t="n">
         <v>5</v>
@@ -3330,16 +3330,16 @@
         <v>3</v>
       </c>
       <c r="AW13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX13" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AY13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ13" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="BA13" t="n">
         <v>1</v>
@@ -3536,28 +3536,28 @@
         <v>2.11</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AT14" t="n">
-        <v>4</v>
+        <v>3.93</v>
       </c>
       <c r="AU14" t="n">
         <v>12</v>
       </c>
       <c r="AV14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX14" t="n">
         <v>9</v>
       </c>
       <c r="AY14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA14" t="n">
         <v>13</v>
@@ -3751,31 +3751,31 @@
         <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="AU15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV15" t="n">
         <v>4</v>
       </c>
       <c r="AW15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY15" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AZ15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA15" t="n">
         <v>3</v>
@@ -3969,13 +3969,13 @@
         <v>3</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.38</v>
+        <v>3.07</v>
       </c>
       <c r="AU16" t="n">
         <v>2</v>
@@ -3984,16 +3984,16 @@
         <v>4</v>
       </c>
       <c r="AW16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX16" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AY16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="BA16" t="n">
         <v>6</v>
@@ -4187,28 +4187,28 @@
         <v>2</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="AS17" t="n">
         <v>1.64</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.89</v>
+        <v>4.01</v>
       </c>
       <c r="AU17" t="n">
         <v>4</v>
       </c>
       <c r="AV17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ17" t="n">
         <v>10</v>
@@ -4405,31 +4405,31 @@
         <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.45</v>
+        <v>1.19</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.47</v>
+        <v>3.14</v>
       </c>
       <c r="AU18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW18" t="n">
         <v>9</v>
       </c>
       <c r="AX18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA18" t="n">
         <v>4</v>
@@ -4623,13 +4623,13 @@
         <v>2</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AS19" t="n">
         <v>0.85</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.41</v>
+        <v>3.35</v>
       </c>
       <c r="AU19" t="n">
         <v>2</v>
@@ -4641,13 +4641,13 @@
         <v>12</v>
       </c>
       <c r="AX19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY19" t="n">
         <v>14</v>
       </c>
       <c r="AZ19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA19" t="n">
         <v>8</v>
@@ -4841,13 +4841,13 @@
         <v>0.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="AS20" t="n">
         <v>0.88</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="AU20" t="n">
         <v>7</v>
@@ -5062,10 +5062,10 @@
         <v>1.21</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AT21" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="AU21" t="n">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP21"/>
+  <dimension ref="A1:BP23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ3" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AQ4" t="n">
         <v>3</v>
@@ -1786,7 +1786,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -3745,10 +3745,10 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR15" t="n">
         <v>2.05</v>
@@ -5086,13 +5086,13 @@
         <v>10</v>
       </c>
       <c r="BA21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB21" t="n">
         <v>3</v>
       </c>
       <c r="BC21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD21" t="n">
         <v>1.92</v>
@@ -5132,6 +5132,442 @@
       </c>
       <c r="BP21" t="n">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="n">
+        <v>7962661</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>45893.375</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Winterthur</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>['12', '60']</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>['68', '90+2']</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>7962662</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>45893.47916666666</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>St. Gallen</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Luzern</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>['3']</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X23" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -5295,13 +5295,13 @@
         <v>11</v>
       </c>
       <c r="AX22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY22" t="n">
         <v>16</v>
       </c>
       <c r="AZ22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA22" t="n">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -5507,7 +5507,7 @@
         <v>8</v>
       </c>
       <c r="AV23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW23" t="n">
         <v>13</v>
@@ -5519,7 +5519,7 @@
         <v>21</v>
       </c>
       <c r="AZ23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA23" t="n">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP23"/>
+  <dimension ref="A1:BP26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,7 +1132,7 @@
         <v>2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AQ8" t="n">
         <v>0.5</v>
@@ -2658,7 +2658,7 @@
         <v>3</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ11" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AQ13" t="n">
         <v>0</v>
@@ -4402,7 +4402,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR18" t="n">
         <v>1.19</v>
@@ -4620,7 +4620,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR19" t="n">
         <v>2.5</v>
@@ -4838,7 +4838,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR20" t="n">
         <v>1.59</v>
@@ -5568,6 +5568,660 @@
       </c>
       <c r="BP23" t="n">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
+        <v>7962669</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>45899.54166666666</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Winterthur</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Zürich</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>['72', '80', '90+5']</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V24" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="n">
+        <v>7962670</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>45899.54166666666</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Thun</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>['50']</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>['84']</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="V25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="n">
+        <v>7962671</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>45899.64583333334</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sion</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Basel</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>['14']</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>4</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="V26" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X26" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP26"/>
+  <dimension ref="A1:BP27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ6" t="n">
         <v>0.33</v>
@@ -4617,7 +4617,7 @@
         <v>1</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ19" t="n">
         <v>2.33</v>
@@ -6222,6 +6222,224 @@
       </c>
       <c r="BP26" t="n">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="n">
+        <v>7962672</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>45900.375</v>
+      </c>
+      <c r="F27" t="n">
+        <v>5</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lausanne Sport</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>St. Gallen</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>['46']</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>['55', '64']</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>1.55</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP27"/>
+  <dimension ref="A1:BP29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1350,7 +1350,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ5" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AQ9" t="n">
         <v>3</v>
@@ -4181,7 +4181,7 @@
         <v>3</v>
       </c>
       <c r="AP17" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ17" t="n">
         <v>2</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AQ20" t="n">
         <v>0.67</v>
@@ -5492,7 +5492,7 @@
         <v>2</v>
       </c>
       <c r="AQ23" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AR23" t="n">
         <v>1.97</v>
@@ -6440,6 +6440,442 @@
       </c>
       <c r="BP27" t="n">
         <v>1.55</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>7962673</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>45900.47916666666</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Young Boys</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Lugano</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2</v>
+      </c>
+      <c r="L28" t="n">
+        <v>3</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" t="n">
+        <v>4</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>['11', '48', '80']</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>['12']</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X28" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="n">
+        <v>7962674</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>45900.47916666666</v>
+      </c>
+      <c r="F29" t="n">
+        <v>5</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Servette</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Luzern</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>2</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2</v>
+      </c>
+      <c r="N29" t="n">
+        <v>4</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>['58', '89']</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>['5', '75']</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V29" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X29" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP29"/>
+  <dimension ref="A1:BP31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ2" t="n">
         <v>2</v>
@@ -1132,7 +1132,7 @@
         <v>2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ11" t="n">
         <v>0</v>
@@ -4402,7 +4402,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AR18" t="n">
         <v>1.19</v>
@@ -5053,7 +5053,7 @@
         <v>3</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ21" t="n">
         <v>3</v>
@@ -5925,7 +5925,7 @@
         <v>0.5</v>
       </c>
       <c r="AP25" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ25" t="n">
         <v>0.67</v>
@@ -6146,7 +6146,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AR26" t="n">
         <v>1.52</v>
@@ -6876,6 +6876,442 @@
       </c>
       <c r="BP29" t="n">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="n">
+        <v>7962675</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>45913.54166666666</v>
+      </c>
+      <c r="F30" t="n">
+        <v>6</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Thun</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Basel</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3</v>
+      </c>
+      <c r="N30" t="n">
+        <v>4</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>['51']</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>['24', '41', '90+8']</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="X30" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="n">
+        <v>7962676</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>45913.54166666666</v>
+      </c>
+      <c r="F31" t="n">
+        <v>6</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Zürich</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Servette</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2</v>
+      </c>
+      <c r="L31" t="n">
+        <v>2</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>['28', '43']</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>['80']</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>1.54</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP31"/>
+  <dimension ref="A1:BP35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.5</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ4" t="n">
         <v>2.33</v>
@@ -2219,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ12" t="n">
         <v>2.33</v>
@@ -3530,7 +3530,7 @@
         <v>3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR14" t="n">
         <v>2.11</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ15" t="n">
         <v>0.33</v>
@@ -3963,7 +3963,7 @@
         <v>3</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ16" t="n">
         <v>3</v>
@@ -4184,7 +4184,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ17" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR17" t="n">
         <v>2.37</v>
@@ -5271,7 +5271,7 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ22" t="n">
         <v>0.33</v>
@@ -5489,7 +5489,7 @@
         <v>3</v>
       </c>
       <c r="AP23" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ23" t="n">
         <v>2.33</v>
@@ -5707,7 +5707,7 @@
         <v>2</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ24" t="n">
         <v>2.33</v>
@@ -7312,6 +7312,878 @@
       </c>
       <c r="BP31" t="n">
         <v>1.54</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="n">
+        <v>7962677</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>45913.64583333334</v>
+      </c>
+      <c r="F32" t="n">
+        <v>6</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>St. Gallen</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Lugano</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>['29']</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V32" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X32" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BI32" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="n">
+        <v>7962678</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>45914.375</v>
+      </c>
+      <c r="F33" t="n">
+        <v>6</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Winterthur</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sion</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3</v>
+      </c>
+      <c r="K33" t="n">
+        <v>4</v>
+      </c>
+      <c r="L33" t="n">
+        <v>2</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3</v>
+      </c>
+      <c r="N33" t="n">
+        <v>5</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>['21', '85']</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>['13', '32', '35']</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="V33" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X33" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="n">
+        <v>7962679</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>45914.47916666666</v>
+      </c>
+      <c r="F34" t="n">
+        <v>6</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Luzern</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Young Boys</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="n">
+        <v>2</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>['60']</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>['54', '64']</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X34" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="BI34" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BJ34" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BM34" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BN34" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="n">
+        <v>7962680</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>45914.47916666666</v>
+      </c>
+      <c r="F35" t="n">
+        <v>6</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Lausanne Sport</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>3</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" t="n">
+        <v>4</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>['40', '68', '74']</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>['76']</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>3</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="V35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X35" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="BI35" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ35" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BK35" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL35" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BM35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BN35" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO35" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BP35" t="n">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP35"/>
+  <dimension ref="A1:BP37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1568,7 +1568,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ7" t="n">
         <v>3</v>
@@ -2876,7 +2876,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ13" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.5</v>
@@ -6143,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ26" t="n">
         <v>1.5</v>
@@ -7236,7 +7236,7 @@
         <v>1</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR31" t="n">
         <v>1.6</v>
@@ -8108,7 +8108,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR35" t="n">
         <v>1.67</v>
@@ -8184,6 +8184,442 @@
       </c>
       <c r="BP35" t="n">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="n">
+        <v>7962659</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>45917.58333333334</v>
+      </c>
+      <c r="F36" t="n">
+        <v>4</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Sion</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Servette</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>2</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>['59', '67']</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>3</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="V36" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X36" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI36" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ36" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BK36" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BL36" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BM36" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BN36" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BO36" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BP36" t="n">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="n">
+        <v>7962663</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>45917.58333333334</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lugano</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Lausanne Sport</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>['13']</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>['51']</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V37" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X37" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH37" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI37" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BJ37" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BK37" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL37" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM37" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BN37" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BO37" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BP37" t="n">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP37"/>
+  <dimension ref="A1:BP43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>2.33</v>
@@ -1350,7 +1350,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ5" t="n">
         <v>1</v>
@@ -1786,7 +1786,7 @@
         <v>1</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2001,10 +2001,10 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2655,10 +2655,10 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2876,7 +2876,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>1</v>
       </c>
       <c r="AP14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ14" t="n">
         <v>1.33</v>
@@ -3748,7 +3748,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR15" t="n">
         <v>2.05</v>
@@ -3966,7 +3966,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ16" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AR16" t="n">
         <v>1.24</v>
@@ -4181,7 +4181,7 @@
         <v>3</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ17" t="n">
         <v>2.33</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.5</v>
@@ -4835,10 +4835,10 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AR20" t="n">
         <v>1.59</v>
@@ -5053,10 +5053,10 @@
         <v>3</v>
       </c>
       <c r="AP21" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AR21" t="n">
         <v>1.21</v>
@@ -5274,7 +5274,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR22" t="n">
         <v>1.7</v>
@@ -5492,7 +5492,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ23" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AR23" t="n">
         <v>1.97</v>
@@ -5928,7 +5928,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AR25" t="n">
         <v>1.52</v>
@@ -6364,7 +6364,7 @@
         <v>1</v>
       </c>
       <c r="AQ27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR27" t="n">
         <v>2</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ28" t="n">
         <v>0</v>
@@ -6797,10 +6797,10 @@
         <v>3</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="AQ29" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AR29" t="n">
         <v>1.79</v>
@@ -7233,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ31" t="n">
         <v>1</v>
@@ -8108,7 +8108,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AR35" t="n">
         <v>1.67</v>
@@ -8541,10 +8541,10 @@
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AR37" t="n">
         <v>1.46</v>
@@ -8620,6 +8620,1314 @@
       </c>
       <c r="BP37" t="n">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="n">
+        <v>7962684</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>45927.54166666666</v>
+      </c>
+      <c r="F38" t="n">
+        <v>7</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Servette</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Winterthur</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>4</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>4</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>['8', '49', '58', '61']</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="V38" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X38" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH38" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI38" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BJ38" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BK38" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BL38" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BM38" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BN38" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BO38" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BP38" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="n">
+        <v>7962681</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>45927.54166666666</v>
+      </c>
+      <c r="F39" t="n">
+        <v>7</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lugano</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>2</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>['56', '74']</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>['70']</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="S39" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U39" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V39" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X39" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH39" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI39" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BJ39" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BK39" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BL39" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BM39" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BN39" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BO39" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BP39" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="n">
+        <v>7962683</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>45927.64583333334</v>
+      </c>
+      <c r="F40" t="n">
+        <v>7</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Zürich</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>St. Gallen</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" t="n">
+        <v>3</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1</v>
+      </c>
+      <c r="N40" t="n">
+        <v>4</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>['58', '64', '73']</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>['22']</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R40" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V40" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X40" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>29</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BH40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI40" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ40" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BK40" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BL40" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BM40" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BN40" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BO40" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BP40" t="n">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="n">
+        <v>7962686</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>45928.375</v>
+      </c>
+      <c r="F41" t="n">
+        <v>7</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Young Boys</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Thun</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>4</v>
+      </c>
+      <c r="M41" t="n">
+        <v>2</v>
+      </c>
+      <c r="N41" t="n">
+        <v>6</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>['64', '66', '80', '90']</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>['52', '72']</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R41" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="V41" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="X41" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH41" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="BI41" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ41" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BK41" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BL41" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BM41" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BN41" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO41" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BP41" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="n">
+        <v>7962685</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>45928.47916666666</v>
+      </c>
+      <c r="F42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Sion</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Lausanne Sport</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="V42" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X42" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BH42" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI42" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ42" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BK42" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BL42" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BM42" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BN42" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO42" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BP42" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="n">
+        <v>7962682</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>45928.47916666666</v>
+      </c>
+      <c r="F43" t="n">
+        <v>7</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Basel</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Luzern</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1</v>
+      </c>
+      <c r="M43" t="n">
+        <v>2</v>
+      </c>
+      <c r="N43" t="n">
+        <v>3</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>['53']</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>['15', '55']</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="R43" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="S43" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="V43" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="X43" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>27</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH43" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ43" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BK43" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BL43" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BM43" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BN43" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BO43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BP43" t="n">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -9437,13 +9437,13 @@
         <v>10</v>
       </c>
       <c r="AX41" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY41" t="n">
         <v>14</v>
       </c>
       <c r="AZ41" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA41" t="n">
         <v>3</v>
@@ -9864,7 +9864,7 @@
         <v>3.69</v>
       </c>
       <c r="AU43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV43" t="n">
         <v>2</v>
@@ -9876,7 +9876,7 @@
         <v>5</v>
       </c>
       <c r="AY43" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ43" t="n">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP43"/>
+  <dimension ref="A1:BP49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ4" t="n">
         <v>2.5</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>0.25</v>
@@ -2004,7 +2004,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2219,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AQ9" t="n">
         <v>2</v>
@@ -3091,10 +3091,10 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>1</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR14" t="n">
         <v>2.11</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AQ15" t="n">
         <v>0.25</v>
@@ -3963,10 +3963,10 @@
         <v>3</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AR16" t="n">
         <v>1.24</v>
@@ -4184,7 +4184,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR17" t="n">
         <v>2.37</v>
@@ -4402,7 +4402,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AR18" t="n">
         <v>1.19</v>
@@ -4617,10 +4617,10 @@
         <v>1</v>
       </c>
       <c r="AP19" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR19" t="n">
         <v>2.5</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AQ20" t="n">
         <v>0.5</v>
@@ -5056,7 +5056,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AR21" t="n">
         <v>1.21</v>
@@ -5271,7 +5271,7 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ22" t="n">
         <v>0.25</v>
@@ -5489,7 +5489,7 @@
         <v>3</v>
       </c>
       <c r="AP23" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AQ23" t="n">
         <v>2.5</v>
@@ -5707,10 +5707,10 @@
         <v>2</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ24" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR24" t="n">
         <v>1.08</v>
@@ -6146,7 +6146,7 @@
         <v>1</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AR26" t="n">
         <v>1.52</v>
@@ -6361,7 +6361,7 @@
         <v>3</v>
       </c>
       <c r="AP27" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ27" t="n">
         <v>2</v>
@@ -6582,7 +6582,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AR28" t="n">
         <v>1.93</v>
@@ -6797,7 +6797,7 @@
         <v>3</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AQ29" t="n">
         <v>2.5</v>
@@ -7018,7 +7018,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AR30" t="n">
         <v>1.75</v>
@@ -7451,10 +7451,10 @@
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AR32" t="n">
         <v>2.08</v>
@@ -7669,10 +7669,10 @@
         <v>2</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ33" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR33" t="n">
         <v>1.07</v>
@@ -7887,10 +7887,10 @@
         <v>0.5</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR34" t="n">
         <v>1.27</v>
@@ -8105,7 +8105,7 @@
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ35" t="n">
         <v>0.5</v>
@@ -8759,7 +8759,7 @@
         <v>0.33</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AQ38" t="n">
         <v>0.25</v>
@@ -9416,7 +9416,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ41" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AR41" t="n">
         <v>1.95</v>
@@ -9928,6 +9928,1314 @@
       </c>
       <c r="BP43" t="n">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="n">
+        <v>7962687</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>45934.54166666666</v>
+      </c>
+      <c r="F44" t="n">
+        <v>8</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Luzern</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sion</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>2</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2</v>
+      </c>
+      <c r="L44" t="n">
+        <v>3</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3</v>
+      </c>
+      <c r="N44" t="n">
+        <v>6</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>['3', '23', '61']</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>['49', '80', '90']</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R44" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U44" t="n">
+        <v>3</v>
+      </c>
+      <c r="V44" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X44" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH44" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="BI44" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ44" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BK44" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BL44" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM44" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BN44" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BO44" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BP44" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="n">
+        <v>7962688</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>45934.54166666666</v>
+      </c>
+      <c r="F45" t="n">
+        <v>8</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>St. Gallen</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Thun</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2</v>
+      </c>
+      <c r="K45" t="n">
+        <v>3</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" t="n">
+        <v>2</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>['35']</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>['19', '44']</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R45" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V45" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X45" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH45" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BI45" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ45" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BK45" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL45" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM45" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BN45" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BO45" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BP45" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="n">
+        <v>7962689</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>45934.64583333334</v>
+      </c>
+      <c r="F46" t="n">
+        <v>8</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Zürich</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>3</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>3</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>['35', '55', '82']</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R46" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V46" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X46" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BG46" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH46" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI46" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ46" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BK46" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BL46" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BM46" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BN46" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BO46" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BP46" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="n">
+        <v>7962690</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>45935.375</v>
+      </c>
+      <c r="F47" t="n">
+        <v>8</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lausanne Sport</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Young Boys</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>2</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>2</v>
+      </c>
+      <c r="L47" t="n">
+        <v>5</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>5</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>['6', '12', '47', '74', '78']</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R47" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S47" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="V47" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X47" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BE47" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF47" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BG47" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH47" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="BI47" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ47" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BK47" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BL47" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BM47" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BN47" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BO47" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BP47" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="n">
+        <v>7962691</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>45935.47916666666</v>
+      </c>
+      <c r="F48" t="n">
+        <v>8</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Winterthur</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Lugano</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" t="n">
+        <v>2</v>
+      </c>
+      <c r="M48" t="n">
+        <v>4</v>
+      </c>
+      <c r="N48" t="n">
+        <v>6</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>['27', '46']</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>['57', '64', '68', '70']</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R48" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V48" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X48" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>29</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF48" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG48" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH48" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="BI48" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ48" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BK48" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BL48" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BM48" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BN48" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BO48" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BP48" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="n">
+        <v>7962695</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>45935.47916666666</v>
+      </c>
+      <c r="F49" t="n">
+        <v>8</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Servette</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Basel</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>2</v>
+      </c>
+      <c r="K49" t="n">
+        <v>2</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>3</v>
+      </c>
+      <c r="N49" t="n">
+        <v>3</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>['5', '41', '59']</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="R49" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V49" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X49" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF49" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BG49" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH49" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI49" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ49" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BK49" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BL49" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM49" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BN49" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BO49" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BP49" t="n">
+        <v>1.52</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -5946,13 +5946,13 @@
         <v>4</v>
       </c>
       <c r="AW25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX25" t="n">
         <v>5</v>
       </c>
       <c r="AY25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ25" t="n">
         <v>9</v>
@@ -6385,13 +6385,13 @@
         <v>5</v>
       </c>
       <c r="AX27" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AY27" t="n">
         <v>9</v>
       </c>
       <c r="AZ27" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BA27" t="n">
         <v>6</v>
@@ -6594,13 +6594,13 @@
         <v>3.79</v>
       </c>
       <c r="AU28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV28" t="n">
         <v>4</v>
       </c>
       <c r="AW28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX28" t="n">
         <v>7</v>
@@ -7021,13 +7021,13 @@
         <v>1.8</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AS30" t="n">
         <v>1.54</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.29</v>
+        <v>3.32</v>
       </c>
       <c r="AU30" t="n">
         <v>5</v>
@@ -7036,16 +7036,16 @@
         <v>8</v>
       </c>
       <c r="AW30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX30" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AY30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ30" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA30" t="n">
         <v>4</v>
@@ -7693,13 +7693,13 @@
         <v>7</v>
       </c>
       <c r="AX33" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AY33" t="n">
         <v>9</v>
       </c>
       <c r="AZ33" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA33" t="n">
         <v>5</v>
@@ -7902,13 +7902,13 @@
         <v>2.83</v>
       </c>
       <c r="AU34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV34" t="n">
         <v>5</v>
       </c>
       <c r="AW34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX34" t="n">
         <v>10</v>
@@ -9204,10 +9204,10 @@
         <v>1.62</v>
       </c>
       <c r="AS40" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AT40" t="n">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="AU40" t="n">
         <v>12</v>
@@ -9216,13 +9216,13 @@
         <v>1</v>
       </c>
       <c r="AW40" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX40" t="n">
         <v>5</v>
       </c>
       <c r="AY40" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ40" t="n">
         <v>6</v>
@@ -9419,13 +9419,13 @@
         <v>2.4</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AS41" t="n">
         <v>1.7</v>
       </c>
       <c r="AT41" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="AU41" t="n">
         <v>4</v>
@@ -10073,13 +10073,13 @@
         <v>2</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AT44" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="AU44" t="n">
         <v>3</v>
@@ -10518,13 +10518,13 @@
         <v>3.07</v>
       </c>
       <c r="AU46" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV46" t="n">
         <v>2</v>
       </c>
       <c r="AW46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX46" t="n">
         <v>10</v>
@@ -11166,10 +11166,10 @@
         <v>1.81</v>
       </c>
       <c r="AS49" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AT49" t="n">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="AU49" t="n">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP49"/>
+  <dimension ref="A1:BP52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1568,7 +1568,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ7" t="n">
         <v>2.4</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ10" t="n">
         <v>0.5</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ11" t="n">
         <v>0.5</v>
@@ -3094,7 +3094,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>1</v>
       </c>
       <c r="AP14" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ14" t="n">
         <v>1</v>
@@ -3748,7 +3748,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AR15" t="n">
         <v>2.05</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.8</v>
@@ -4620,7 +4620,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AR19" t="n">
         <v>2.5</v>
@@ -5274,7 +5274,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AR22" t="n">
         <v>1.7</v>
@@ -5710,7 +5710,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AR24" t="n">
         <v>1.08</v>
@@ -5925,7 +5925,7 @@
         <v>0.5</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ25" t="n">
         <v>0.5</v>
@@ -7015,7 +7015,7 @@
         <v>1</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ30" t="n">
         <v>1.8</v>
@@ -7236,7 +7236,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR31" t="n">
         <v>1.6</v>
@@ -8326,7 +8326,7 @@
         <v>1</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR36" t="n">
         <v>1.2</v>
@@ -8541,7 +8541,7 @@
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ37" t="n">
         <v>0.5</v>
@@ -8762,7 +8762,7 @@
         <v>1</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AR38" t="n">
         <v>1.89</v>
@@ -8977,7 +8977,7 @@
         <v>0.67</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ39" t="n">
         <v>0.5</v>
@@ -9849,7 +9849,7 @@
         <v>2.33</v>
       </c>
       <c r="AP43" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ43" t="n">
         <v>2.5</v>
@@ -10506,7 +10506,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AR46" t="n">
         <v>1.62</v>
@@ -11236,6 +11236,660 @@
       </c>
       <c r="BP49" t="n">
         <v>1.52</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="n">
+        <v>7962713</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>45948.54166666666</v>
+      </c>
+      <c r="F50" t="n">
+        <v>9</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Basel</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Winterthur</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>3</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>3</v>
+      </c>
+      <c r="L50" t="n">
+        <v>3</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>3</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>['4', '30', '33']</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R50" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="S50" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="U50" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="X50" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>30</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF50" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BG50" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH50" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="BI50" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ50" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK50" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BL50" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM50" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN50" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BO50" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP50" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="n">
+        <v>7962703</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>45948.54166666666</v>
+      </c>
+      <c r="F51" t="n">
+        <v>9</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Thun</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Servette</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>2</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
+        <v>3</v>
+      </c>
+      <c r="L51" t="n">
+        <v>3</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1</v>
+      </c>
+      <c r="N51" t="n">
+        <v>4</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>['7', '18', '90+3']</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>['6']</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R51" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="S51" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U51" t="n">
+        <v>4</v>
+      </c>
+      <c r="V51" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="X51" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD51" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BE51" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF51" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BG51" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH51" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI51" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ51" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BK51" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BL51" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BM51" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BN51" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BO51" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BP51" t="n">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="n">
+        <v>7962714</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>45948.64583333334</v>
+      </c>
+      <c r="F52" t="n">
+        <v>9</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Lugano</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Zürich</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" t="n">
+        <v>1</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>['25']</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R52" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S52" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U52" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V52" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X52" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BE52" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF52" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BG52" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH52" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI52" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ52" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="BK52" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM52" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN52" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BO52" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP52" t="n">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP52"/>
+  <dimension ref="A1:BP53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AQ4" t="n">
         <v>2.5</v>
@@ -4184,7 +4184,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AR17" t="n">
         <v>2.37</v>
@@ -5271,7 +5271,7 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AQ22" t="n">
         <v>0.2</v>
@@ -7672,7 +7672,7 @@
         <v>0.25</v>
       </c>
       <c r="AQ33" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AR33" t="n">
         <v>1.07</v>
@@ -8105,7 +8105,7 @@
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AQ35" t="n">
         <v>0.5</v>
@@ -10070,7 +10070,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ44" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AR44" t="n">
         <v>1.24</v>
@@ -10503,7 +10503,7 @@
         <v>2.33</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AQ46" t="n">
         <v>1.4</v>
@@ -11890,6 +11890,224 @@
       </c>
       <c r="BP52" t="n">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="n">
+        <v>7962715</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>45949.375</v>
+      </c>
+      <c r="F53" t="n">
+        <v>9</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sion</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1</v>
+      </c>
+      <c r="N53" t="n">
+        <v>1</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>['61']</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R53" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S53" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V53" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X53" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD53" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BE53" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF53" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG53" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH53" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="BI53" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ53" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BK53" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BL53" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BM53" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BN53" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BO53" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BP53" t="n">
+        <v>1.47</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP53"/>
+  <dimension ref="A1:BP55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AQ5" t="n">
         <v>0.75</v>
@@ -2440,7 +2440,7 @@
         <v>1</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2876,7 +2876,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.4</v>
@@ -3963,7 +3963,7 @@
         <v>3</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AQ16" t="n">
         <v>2.4</v>
@@ -4181,7 +4181,7 @@
         <v>3</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AQ17" t="n">
         <v>2.2</v>
@@ -6364,7 +6364,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AR27" t="n">
         <v>2</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AQ28" t="n">
         <v>0.75</v>
@@ -7887,7 +7887,7 @@
         <v>0.5</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AQ34" t="n">
         <v>1</v>
@@ -8108,7 +8108,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AR35" t="n">
         <v>1.67</v>
@@ -8544,7 +8544,7 @@
         <v>2</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AR37" t="n">
         <v>1.46</v>
@@ -9198,7 +9198,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ40" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AR40" t="n">
         <v>1.62</v>
@@ -9413,7 +9413,7 @@
         <v>3</v>
       </c>
       <c r="AP41" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AQ41" t="n">
         <v>2.4</v>
@@ -9634,7 +9634,7 @@
         <v>1</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AR42" t="n">
         <v>1.11</v>
@@ -10067,7 +10067,7 @@
         <v>2.33</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AQ44" t="n">
         <v>2.2</v>
@@ -12108,6 +12108,442 @@
       </c>
       <c r="BP53" t="n">
         <v>1.47</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="n">
+        <v>7962716</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>45949.47916666666</v>
+      </c>
+      <c r="F54" t="n">
+        <v>9</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Luzern</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Lausanne Sport</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>2</v>
+      </c>
+      <c r="M54" t="n">
+        <v>2</v>
+      </c>
+      <c r="N54" t="n">
+        <v>4</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>['84', '90']</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>['53', '74']</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R54" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="S54" t="n">
+        <v>3</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U54" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V54" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X54" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD54" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BE54" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF54" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BG54" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH54" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="BI54" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ54" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK54" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BL54" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BM54" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BN54" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BO54" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BP54" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="n">
+        <v>7962717</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>45949.47916666666</v>
+      </c>
+      <c r="F55" t="n">
+        <v>9</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Young Boys</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>St. Gallen</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>1</v>
+      </c>
+      <c r="M55" t="n">
+        <v>2</v>
+      </c>
+      <c r="N55" t="n">
+        <v>3</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>['85']</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>['56', '87']</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="R55" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S55" t="n">
+        <v>4</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V55" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="X55" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD55" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BE55" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BF55" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BG55" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH55" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="BI55" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ55" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BK55" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BL55" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BM55" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BN55" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BO55" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BP55" t="n">
+        <v>1.58</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP55"/>
+  <dimension ref="A1:BP58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.8</v>
@@ -1350,7 +1350,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AQ8" t="n">
         <v>1</v>
@@ -2658,7 +2658,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AQ13" t="n">
         <v>0.75</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ15" t="n">
         <v>0.2</v>
@@ -3966,7 +3966,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ16" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AR16" t="n">
         <v>1.24</v>
@@ -4838,7 +4838,7 @@
         <v>1</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AR20" t="n">
         <v>1.59</v>
@@ -5056,7 +5056,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AR21" t="n">
         <v>1.21</v>
@@ -5489,10 +5489,10 @@
         <v>3</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ23" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AR23" t="n">
         <v>1.97</v>
@@ -5707,7 +5707,7 @@
         <v>2</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AQ24" t="n">
         <v>1.4</v>
@@ -5928,7 +5928,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AR25" t="n">
         <v>1.52</v>
@@ -6143,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AQ26" t="n">
         <v>1.8</v>
@@ -6800,7 +6800,7 @@
         <v>1</v>
       </c>
       <c r="AQ29" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AR29" t="n">
         <v>1.79</v>
@@ -7451,7 +7451,7 @@
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ32" t="n">
         <v>0.75</v>
@@ -7669,7 +7669,7 @@
         <v>2</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AQ33" t="n">
         <v>2.2</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AQ36" t="n">
         <v>0.75</v>
@@ -8980,7 +8980,7 @@
         <v>2</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AR39" t="n">
         <v>1.4</v>
@@ -9416,7 +9416,7 @@
         <v>2</v>
       </c>
       <c r="AQ41" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AR41" t="n">
         <v>1.93</v>
@@ -9631,7 +9631,7 @@
         <v>0.33</v>
       </c>
       <c r="AP42" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AQ42" t="n">
         <v>0.6</v>
@@ -9852,7 +9852,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ43" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AR43" t="n">
         <v>2.38</v>
@@ -10285,10 +10285,10 @@
         <v>2.25</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ45" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AR45" t="n">
         <v>1.92</v>
@@ -10939,7 +10939,7 @@
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AQ48" t="n">
         <v>0.75</v>
@@ -12544,6 +12544,660 @@
       </c>
       <c r="BP55" t="n">
         <v>1.58</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="n">
+        <v>7962718</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>45955.54166666666</v>
+      </c>
+      <c r="F56" t="n">
+        <v>10</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Sion</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Thun</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N56" t="n">
+        <v>1</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>['12']</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="R56" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S56" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U56" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V56" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X56" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BE56" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF56" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG56" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BH56" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BI56" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BJ56" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BK56" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BL56" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BM56" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BN56" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BO56" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BP56" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="n">
+        <v>7962719</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>45955.54166666666</v>
+      </c>
+      <c r="F57" t="n">
+        <v>10</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>St. Gallen</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>3</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>3</v>
+      </c>
+      <c r="L57" t="n">
+        <v>5</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>5</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>['10', '15', '29', '72', '90+2']</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R57" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S57" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U57" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V57" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X57" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC57" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD57" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BE57" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF57" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BG57" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH57" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI57" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ57" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK57" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BL57" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BM57" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BN57" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BO57" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BP57" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="n">
+        <v>8125647</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>45955.64583333334</v>
+      </c>
+      <c r="F58" t="n">
+        <v>10</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Winterthur</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Luzern</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>2</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>2</v>
+      </c>
+      <c r="L58" t="n">
+        <v>2</v>
+      </c>
+      <c r="M58" t="n">
+        <v>2</v>
+      </c>
+      <c r="N58" t="n">
+        <v>4</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>['13', '22']</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>['65', '90+1']</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="R58" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S58" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U58" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V58" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X58" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AQ58" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AT58" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AU58" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV58" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW58" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX58" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY58" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ58" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA58" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB58" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC58" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD58" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BE58" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF58" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BG58" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH58" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="BI58" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ58" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BK58" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BL58" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BM58" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN58" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BO58" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BP58" t="n">
+        <v>1.55</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -13152,13 +13152,13 @@
         <v>14</v>
       </c>
       <c r="BA58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BB58" t="n">
         <v>5</v>
       </c>
       <c r="BC58" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BD58" t="n">
         <v>2.46</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -13152,13 +13152,13 @@
         <v>14</v>
       </c>
       <c r="BA58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BB58" t="n">
         <v>5</v>
       </c>
       <c r="BC58" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BD58" t="n">
         <v>2.46</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP58"/>
+  <dimension ref="A1:BP61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AQ2" t="n">
         <v>2.2</v>
@@ -1132,7 +1132,7 @@
         <v>2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AQ6" t="n">
         <v>0.2</v>
@@ -2222,7 +2222,7 @@
         <v>0.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ9" t="n">
         <v>2.25</v>
@@ -3312,7 +3312,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR14" t="n">
         <v>2.11</v>
@@ -4402,7 +4402,7 @@
         <v>2</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AR18" t="n">
         <v>1.19</v>
@@ -4617,7 +4617,7 @@
         <v>1</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AQ19" t="n">
         <v>1.4</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ20" t="n">
         <v>0.4</v>
@@ -5053,7 +5053,7 @@
         <v>3</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AQ21" t="n">
         <v>2.5</v>
@@ -6146,7 +6146,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AR26" t="n">
         <v>1.52</v>
@@ -6361,7 +6361,7 @@
         <v>3</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AQ27" t="n">
         <v>2.25</v>
@@ -6582,7 +6582,7 @@
         <v>2</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AR28" t="n">
         <v>1.93</v>
@@ -6797,7 +6797,7 @@
         <v>3</v>
       </c>
       <c r="AP29" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ29" t="n">
         <v>2.2</v>
@@ -7018,7 +7018,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AR30" t="n">
         <v>1.78</v>
@@ -7233,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AQ31" t="n">
         <v>0.75</v>
@@ -7454,7 +7454,7 @@
         <v>2</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AR32" t="n">
         <v>2.08</v>
@@ -7890,7 +7890,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR34" t="n">
         <v>1.27</v>
@@ -8759,7 +8759,7 @@
         <v>0.33</v>
       </c>
       <c r="AP38" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ38" t="n">
         <v>0.2</v>
@@ -9195,7 +9195,7 @@
         <v>3</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AQ40" t="n">
         <v>2.25</v>
@@ -10721,10 +10721,10 @@
         <v>1.33</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR47" t="n">
         <v>1.67</v>
@@ -10942,7 +10942,7 @@
         <v>0.4</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AR48" t="n">
         <v>1.09</v>
@@ -11157,10 +11157,10 @@
         <v>1.5</v>
       </c>
       <c r="AP49" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AR49" t="n">
         <v>1.81</v>
@@ -13198,6 +13198,660 @@
       </c>
       <c r="BP58" t="n">
         <v>1.55</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="n">
+        <v>7962720</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>45956.41666666666</v>
+      </c>
+      <c r="F59" t="n">
+        <v>10</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Zürich</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Young Boys</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>2</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" t="n">
+        <v>3</v>
+      </c>
+      <c r="L59" t="n">
+        <v>2</v>
+      </c>
+      <c r="M59" t="n">
+        <v>3</v>
+      </c>
+      <c r="N59" t="n">
+        <v>5</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>['38', '42']</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>['14', '48', '54']</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R59" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S59" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U59" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V59" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W59" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X59" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP59" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ59" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR59" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AT59" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AU59" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV59" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW59" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX59" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY59" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ59" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA59" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB59" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC59" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD59" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BE59" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF59" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG59" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BH59" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI59" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ59" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BK59" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BL59" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BM59" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BN59" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BO59" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BP59" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="n">
+        <v>7962721</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>45956.52083333334</v>
+      </c>
+      <c r="F60" t="n">
+        <v>10</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Lausanne Sport</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Basel</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>3</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>3</v>
+      </c>
+      <c r="L60" t="n">
+        <v>5</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1</v>
+      </c>
+      <c r="N60" t="n">
+        <v>6</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>['6', '17', '35', '55', '66']</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>['85']</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="R60" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="S60" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U60" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V60" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W60" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="X60" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AI60" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP60" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ60" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR60" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AT60" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AU60" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV60" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW60" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX60" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY60" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ60" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA60" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB60" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC60" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD60" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BE60" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF60" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG60" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH60" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI60" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ60" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BK60" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BL60" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BM60" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BN60" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO60" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BP60" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="n">
+        <v>7962722</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>45956.52083333334</v>
+      </c>
+      <c r="F61" t="n">
+        <v>10</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Servette</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Lugano</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="n">
+        <v>2</v>
+      </c>
+      <c r="L61" t="n">
+        <v>2</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1</v>
+      </c>
+      <c r="N61" t="n">
+        <v>3</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>['11', '82']</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>['37']</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R61" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S61" t="n">
+        <v>3</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U61" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V61" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W61" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X61" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AJ61" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP61" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ61" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AR61" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AS61" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT61" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="AU61" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV61" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW61" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX61" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY61" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ61" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA61" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB61" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC61" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD61" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BE61" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF61" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BG61" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BH61" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI61" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ61" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BK61" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BL61" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BM61" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BN61" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO61" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BP61" t="n">
+        <v>1.47</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -13591,10 +13591,10 @@
         <v>4</v>
       </c>
       <c r="BB60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD60" t="n">
         <v>2.69</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -13591,10 +13591,10 @@
         <v>4</v>
       </c>
       <c r="BB60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC60" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD60" t="n">
         <v>2.69</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP61"/>
+  <dimension ref="A1:BP63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1786,7 +1786,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ11" t="n">
         <v>0.6</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AQ13" t="n">
         <v>0.6</v>
@@ -3748,7 +3748,7 @@
         <v>2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR15" t="n">
         <v>2.05</v>
@@ -5274,7 +5274,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR22" t="n">
         <v>1.7</v>
@@ -5925,7 +5925,7 @@
         <v>0.5</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ25" t="n">
         <v>0.4</v>
@@ -6143,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AQ26" t="n">
         <v>1.5</v>
@@ -6364,7 +6364,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ27" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AR27" t="n">
         <v>2</v>
@@ -7015,7 +7015,7 @@
         <v>1</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ30" t="n">
         <v>1.5</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AQ36" t="n">
         <v>0.75</v>
@@ -8762,7 +8762,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR38" t="n">
         <v>1.89</v>
@@ -9198,7 +9198,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ40" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AR40" t="n">
         <v>1.62</v>
@@ -9631,7 +9631,7 @@
         <v>0.33</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AQ42" t="n">
         <v>0.6</v>
@@ -11378,7 +11378,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR50" t="n">
         <v>2.4</v>
@@ -11593,7 +11593,7 @@
         <v>1</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ51" t="n">
         <v>0.75</v>
@@ -12468,7 +12468,7 @@
         <v>2</v>
       </c>
       <c r="AQ55" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AR55" t="n">
         <v>1.78</v>
@@ -12683,7 +12683,7 @@
         <v>2.4</v>
       </c>
       <c r="AP56" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AQ56" t="n">
         <v>2.5</v>
@@ -13143,13 +13143,13 @@
         <v>6</v>
       </c>
       <c r="AX58" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY58" t="n">
         <v>11</v>
       </c>
       <c r="AZ58" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA58" t="n">
         <v>3</v>
@@ -13579,13 +13579,13 @@
         <v>10</v>
       </c>
       <c r="AX60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY60" t="n">
         <v>22</v>
       </c>
       <c r="AZ60" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA60" t="n">
         <v>4</v>
@@ -13852,6 +13852,442 @@
       </c>
       <c r="BP61" t="n">
         <v>1.47</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="n">
+        <v>7962725</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>45958.6875</v>
+      </c>
+      <c r="F62" t="n">
+        <v>11</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Sion</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>St. Gallen</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>3</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" t="n">
+        <v>4</v>
+      </c>
+      <c r="L62" t="n">
+        <v>3</v>
+      </c>
+      <c r="M62" t="n">
+        <v>2</v>
+      </c>
+      <c r="N62" t="n">
+        <v>5</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>['9', '42', '45+3']</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>['5', '89']</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="R62" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="S62" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U62" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V62" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="W62" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X62" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AJ62" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK62" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AL62" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AO62" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AP62" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ62" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR62" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AS62" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AT62" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AU62" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV62" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW62" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX62" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY62" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ62" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA62" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB62" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC62" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD62" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BE62" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF62" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BG62" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH62" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI62" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BJ62" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BK62" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BL62" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BM62" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BN62" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO62" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BP62" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="n">
+        <v>7962726</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>45958.6875</v>
+      </c>
+      <c r="F63" t="n">
+        <v>11</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Thun</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Winterthur</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>2</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>2</v>
+      </c>
+      <c r="L63" t="n">
+        <v>3</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>3</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>['20', '36', '82']</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R63" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S63" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U63" t="n">
+        <v>4</v>
+      </c>
+      <c r="V63" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="W63" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X63" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AI63" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AJ63" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK63" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AL63" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AM63" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO63" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AP63" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ63" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AR63" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS63" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AT63" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AU63" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV63" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW63" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX63" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY63" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ63" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA63" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB63" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC63" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD63" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BE63" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF63" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="BG63" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH63" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BI63" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ63" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BK63" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BL63" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BM63" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BN63" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BO63" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BP63" t="n">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP63"/>
+  <dimension ref="A1:BP67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1568,7 +1568,7 @@
         <v>2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>0.17</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ7" t="n">
         <v>2.5</v>
@@ -2222,7 +2222,7 @@
         <v>0.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AQ10" t="n">
         <v>0.4</v>
@@ -3094,7 +3094,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3527,10 +3527,10 @@
         <v>1</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR14" t="n">
         <v>2.11</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.5</v>
@@ -4617,10 +4617,10 @@
         <v>1</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR19" t="n">
         <v>2.5</v>
@@ -5271,7 +5271,7 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ22" t="n">
         <v>0.17</v>
@@ -5492,7 +5492,7 @@
         <v>2</v>
       </c>
       <c r="AQ23" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AR23" t="n">
         <v>1.97</v>
@@ -5710,7 +5710,7 @@
         <v>0.4</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR24" t="n">
         <v>1.08</v>
@@ -6361,7 +6361,7 @@
         <v>3</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.8</v>
@@ -6800,7 +6800,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ29" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AR29" t="n">
         <v>1.79</v>
@@ -7236,7 +7236,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AR31" t="n">
         <v>1.6</v>
@@ -7890,7 +7890,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR34" t="n">
         <v>1.27</v>
@@ -8105,7 +8105,7 @@
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ35" t="n">
         <v>0.6</v>
@@ -8326,7 +8326,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AR36" t="n">
         <v>1.2</v>
@@ -8541,7 +8541,7 @@
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ37" t="n">
         <v>0.6</v>
@@ -8977,7 +8977,7 @@
         <v>0.67</v>
       </c>
       <c r="AP39" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ39" t="n">
         <v>0.4</v>
@@ -9849,10 +9849,10 @@
         <v>2.33</v>
       </c>
       <c r="AP43" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AQ43" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AR43" t="n">
         <v>2.38</v>
@@ -10503,10 +10503,10 @@
         <v>2.33</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR46" t="n">
         <v>1.62</v>
@@ -10721,10 +10721,10 @@
         <v>1.33</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR47" t="n">
         <v>1.67</v>
@@ -11375,7 +11375,7 @@
         <v>0.25</v>
       </c>
       <c r="AP50" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AQ50" t="n">
         <v>0.17</v>
@@ -11596,7 +11596,7 @@
         <v>2</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AR51" t="n">
         <v>1.87</v>
@@ -11811,10 +11811,10 @@
         <v>1.75</v>
       </c>
       <c r="AP52" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AR52" t="n">
         <v>1.37</v>
@@ -12029,7 +12029,7 @@
         <v>2</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ53" t="n">
         <v>2.2</v>
@@ -13122,7 +13122,7 @@
         <v>0.4</v>
       </c>
       <c r="AQ58" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AR58" t="n">
         <v>1.1</v>
@@ -13340,7 +13340,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR59" t="n">
         <v>1.96</v>
@@ -13555,7 +13555,7 @@
         <v>1.8</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AQ60" t="n">
         <v>1.5</v>
@@ -14288,6 +14288,878 @@
       </c>
       <c r="BP63" t="n">
         <v>1.31</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="n">
+        <v>7962723</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>45959.6875</v>
+      </c>
+      <c r="F64" t="n">
+        <v>11</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Lausanne Sport</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Servette</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>1</v>
+      </c>
+      <c r="M64" t="n">
+        <v>3</v>
+      </c>
+      <c r="N64" t="n">
+        <v>4</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>['57']</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>['49', '76', '90+4']</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R64" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S64" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="U64" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V64" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W64" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X64" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ64" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK64" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP64" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ64" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR64" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AS64" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AT64" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AU64" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV64" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW64" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX64" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY64" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ64" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA64" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB64" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC64" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD64" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BE64" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BF64" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BG64" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BH64" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BI64" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BJ64" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BK64" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BL64" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BM64" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BN64" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BO64" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BP64" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="n">
+        <v>7962724</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>45959.6875</v>
+      </c>
+      <c r="F65" t="n">
+        <v>11</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Basel</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Zürich</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1</v>
+      </c>
+      <c r="L65" t="n">
+        <v>2</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>2</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>['13', '50']</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R65" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="U65" t="n">
+        <v>4</v>
+      </c>
+      <c r="V65" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X65" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ65" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AQ65" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AR65" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AS65" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AT65" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU65" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV65" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW65" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX65" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY65" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ65" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA65" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB65" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC65" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD65" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BE65" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF65" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BG65" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BH65" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="BI65" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BJ65" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BK65" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BL65" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BM65" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BN65" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BO65" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BP65" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="n">
+        <v>7962727</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>45960.6875</v>
+      </c>
+      <c r="F66" t="n">
+        <v>11</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Lugano</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Luzern</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>2</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>2</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>['52', '63']</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R66" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S66" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U66" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V66" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W66" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X66" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AP66" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AQ66" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AR66" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AT66" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AU66" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV66" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW66" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX66" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY66" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ66" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB66" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC66" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD66" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BE66" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF66" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BG66" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH66" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BI66" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ66" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BK66" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BL66" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM66" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BN66" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO66" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP66" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="n">
+        <v>7962728</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>45960.6875</v>
+      </c>
+      <c r="F67" t="n">
+        <v>11</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Young Boys</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>2</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1</v>
+      </c>
+      <c r="K67" t="n">
+        <v>3</v>
+      </c>
+      <c r="L67" t="n">
+        <v>3</v>
+      </c>
+      <c r="M67" t="n">
+        <v>3</v>
+      </c>
+      <c r="N67" t="n">
+        <v>6</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>['16', '25', '74']</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>['27', '67', '89']</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R67" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S67" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U67" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V67" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="W67" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X67" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ67" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ67" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR67" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS67" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AT67" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU67" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV67" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW67" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX67" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY67" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ67" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA67" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC67" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD67" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BE67" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF67" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BG67" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH67" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="BI67" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ67" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BK67" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BL67" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BM67" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BN67" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BO67" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BP67" t="n">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP67"/>
+  <dimension ref="A1:BP72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
         <v>2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.33</v>
@@ -2658,7 +2658,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.17</v>
@@ -3963,7 +3963,7 @@
         <v>3</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AQ16" t="n">
         <v>2.5</v>
@@ -4181,10 +4181,10 @@
         <v>3</v>
       </c>
       <c r="AP17" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ17" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AR17" t="n">
         <v>2.37</v>
@@ -4402,7 +4402,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR18" t="n">
         <v>1.19</v>
@@ -4838,7 +4838,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AR20" t="n">
         <v>1.59</v>
@@ -5053,7 +5053,7 @@
         <v>3</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AQ21" t="n">
         <v>2.5</v>
@@ -5707,7 +5707,7 @@
         <v>2</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AQ24" t="n">
         <v>1.17</v>
@@ -5925,10 +5925,10 @@
         <v>0.5</v>
       </c>
       <c r="AP25" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AR25" t="n">
         <v>1.52</v>
@@ -6146,7 +6146,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR26" t="n">
         <v>1.52</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ28" t="n">
         <v>0.6</v>
@@ -7015,10 +7015,10 @@
         <v>1</v>
       </c>
       <c r="AP30" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR30" t="n">
         <v>1.78</v>
@@ -7233,10 +7233,10 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AR31" t="n">
         <v>1.6</v>
@@ -7669,10 +7669,10 @@
         <v>2</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AQ33" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AR33" t="n">
         <v>1.07</v>
@@ -7887,7 +7887,7 @@
         <v>0.5</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AQ34" t="n">
         <v>1.33</v>
@@ -8108,7 +8108,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AR35" t="n">
         <v>1.67</v>
@@ -8326,7 +8326,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AR36" t="n">
         <v>1.2</v>
@@ -8544,7 +8544,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AR37" t="n">
         <v>1.46</v>
@@ -8980,7 +8980,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AR39" t="n">
         <v>1.4</v>
@@ -9195,7 +9195,7 @@
         <v>3</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AQ40" t="n">
         <v>1.8</v>
@@ -9413,7 +9413,7 @@
         <v>3</v>
       </c>
       <c r="AP41" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ41" t="n">
         <v>2.5</v>
@@ -9634,7 +9634,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AR42" t="n">
         <v>1.11</v>
@@ -10067,10 +10067,10 @@
         <v>2.33</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AQ44" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AR44" t="n">
         <v>1.24</v>
@@ -10939,7 +10939,7 @@
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AQ48" t="n">
         <v>0.6</v>
@@ -11160,7 +11160,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR49" t="n">
         <v>1.81</v>
@@ -11593,10 +11593,10 @@
         <v>1</v>
       </c>
       <c r="AP51" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AR51" t="n">
         <v>1.87</v>
@@ -12032,7 +12032,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ53" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AR53" t="n">
         <v>1.56</v>
@@ -12247,10 +12247,10 @@
         <v>0.5</v>
       </c>
       <c r="AP54" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AR54" t="n">
         <v>1.29</v>
@@ -12465,7 +12465,7 @@
         <v>2</v>
       </c>
       <c r="AP55" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ55" t="n">
         <v>1.8</v>
@@ -12904,7 +12904,7 @@
         <v>2</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AR57" t="n">
         <v>1.87</v>
@@ -13119,7 +13119,7 @@
         <v>2.5</v>
       </c>
       <c r="AP58" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AQ58" t="n">
         <v>1.83</v>
@@ -13337,7 +13337,7 @@
         <v>1</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AQ59" t="n">
         <v>1.33</v>
@@ -13558,7 +13558,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR60" t="n">
         <v>1.75</v>
@@ -14209,7 +14209,7 @@
         <v>0.2</v>
       </c>
       <c r="AP63" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ63" t="n">
         <v>0.17</v>
@@ -14430,7 +14430,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AR64" t="n">
         <v>1.88</v>
@@ -15105,13 +15105,13 @@
         <v>9</v>
       </c>
       <c r="AX67" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY67" t="n">
         <v>17</v>
       </c>
       <c r="AZ67" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA67" t="n">
         <v>5</v>
@@ -15160,6 +15160,1096 @@
       </c>
       <c r="BP67" t="n">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="n">
+        <v>7962730</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>45962.58333333334</v>
+      </c>
+      <c r="F68" t="n">
+        <v>12</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Winterthur</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Servette</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1</v>
+      </c>
+      <c r="L68" t="n">
+        <v>4</v>
+      </c>
+      <c r="M68" t="n">
+        <v>2</v>
+      </c>
+      <c r="N68" t="n">
+        <v>6</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>['52', '54', '69', '90+3']</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>['40', '90+1']</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>5</v>
+      </c>
+      <c r="R68" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="S68" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U68" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="V68" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W68" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X68" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AT68" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AU68" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV68" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW68" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX68" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY68" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ68" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA68" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB68" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC68" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD68" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BE68" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF68" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BG68" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH68" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI68" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ68" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BK68" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BL68" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BM68" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BN68" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BO68" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BP68" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="n">
+        <v>7962733</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>45962.58333333334</v>
+      </c>
+      <c r="F69" t="n">
+        <v>12</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Thun</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Sion</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" t="n">
+        <v>1</v>
+      </c>
+      <c r="K69" t="n">
+        <v>2</v>
+      </c>
+      <c r="L69" t="n">
+        <v>2</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1</v>
+      </c>
+      <c r="N69" t="n">
+        <v>3</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>['39', '65']</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>['15']</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R69" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S69" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U69" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V69" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W69" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X69" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="AU69" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV69" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW69" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX69" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY69" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ69" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA69" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB69" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC69" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD69" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BE69" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF69" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BG69" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH69" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BI69" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ69" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BK69" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL69" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BM69" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BN69" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO69" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP69" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="n">
+        <v>7962734</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>45962.6875</v>
+      </c>
+      <c r="F70" t="n">
+        <v>12</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Zürich</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Lausanne Sport</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" t="n">
+        <v>2</v>
+      </c>
+      <c r="L70" t="n">
+        <v>1</v>
+      </c>
+      <c r="M70" t="n">
+        <v>2</v>
+      </c>
+      <c r="N70" t="n">
+        <v>3</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>['32']</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>['10', '82']</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R70" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="S70" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U70" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V70" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W70" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X70" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AP70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR70" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AS70" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AT70" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AU70" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV70" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW70" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX70" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY70" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ70" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA70" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB70" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC70" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD70" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BE70" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF70" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BG70" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BH70" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="BI70" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BJ70" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BK70" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BL70" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BM70" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BN70" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BO70" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BP70" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="n">
+        <v>7962731</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>45963.52083333334</v>
+      </c>
+      <c r="F71" t="n">
+        <v>12</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Young Boys</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Basel</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R71" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S71" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U71" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V71" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W71" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="X71" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AJ71" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK71" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP71" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AQ71" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR71" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS71" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AT71" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AU71" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW71" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX71" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY71" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ71" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA71" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB71" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC71" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD71" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BE71" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF71" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BG71" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH71" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="BI71" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ71" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="BK71" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL71" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM71" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN71" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO71" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BP71" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="n">
+        <v>7962732</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>45963.52083333334</v>
+      </c>
+      <c r="F72" t="n">
+        <v>12</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Luzern</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>3</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>3</v>
+      </c>
+      <c r="L72" t="n">
+        <v>6</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="n">
+        <v>6</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>['18', '27', '40', '66', '71', '73']</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R72" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S72" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U72" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V72" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W72" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X72" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ72" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK72" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AO72" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AP72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ72" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AR72" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS72" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AT72" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AU72" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV72" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW72" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX72" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY72" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ72" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA72" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB72" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC72" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD72" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BE72" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF72" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG72" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH72" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BI72" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ72" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BK72" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BL72" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BM72" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BN72" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BO72" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BP72" t="n">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -2959,7 +2959,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>7962657</v>
+        <v>8125646</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2979,110 +2979,110 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>['72']</t>
+          <t>['6', '42', '60', '80']</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>['78']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
         <v>0</v>
@@ -3091,10 +3091,10 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.17</v>
+        <v>0.6</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3106,70 +3106,70 @@
         <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AV12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AX12" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="AY12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ12" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC12" t="n">
         <v>5</v>
       </c>
-      <c r="BA12" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>9</v>
-      </c>
       <c r="BD12" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BH12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BO12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BP12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3177,7 +3177,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>8125646</v>
+        <v>7962657</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -3197,197 +3197,197 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
         <v>2</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>['72']</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>['78']</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V13" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV13" t="n">
         <v>2</v>
       </c>
-      <c r="L13" t="n">
+      <c r="AW13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA13" t="n">
         <v>4</v>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>['6', '42', '60', '80']</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
+      <c r="BB13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BG13" t="n">
         <v>1.17</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>0</v>
-      </c>
       <c r="BH13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BK13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BL13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BM13" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BO13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BP13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="14">
@@ -4267,7 +4267,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>7962668</v>
+        <v>8125649</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -4287,167 +4287,167 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
         <v>2</v>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>3</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>4</v>
-      </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>['11', '31', '90+6']</t>
+          <t>['74']</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>['63']</t>
+          <t>['33']</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>3.65</v>
+        <v>2.25</v>
       </c>
       <c r="R18" t="n">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="S18" t="n">
-        <v>2.4</v>
+        <v>4.41</v>
       </c>
       <c r="T18" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="U18" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="V18" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="W18" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="X18" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y18" t="n">
         <v>1.13</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.51</v>
+        <v>1.72</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.74</v>
+        <v>3.63</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.76</v>
+        <v>3.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AD18" t="n">
         <v>13</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF18" t="n">
-        <v>4.55</v>
+        <v>4.33</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.48</v>
+        <v>2.15</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.62</v>
+        <v>2.23</v>
       </c>
       <c r="AK18" t="n">
         <v>1.25</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AM18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
         <v>1.33</v>
       </c>
-      <c r="AN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>2.17</v>
-      </c>
       <c r="AQ18" t="n">
-        <v>1.43</v>
+        <v>0.33</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.19</v>
+        <v>1.59</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.95</v>
+        <v>0.88</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.14</v>
+        <v>2.47</v>
       </c>
       <c r="AU18" t="n">
         <v>7</v>
       </c>
       <c r="AV18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX18" t="n">
         <v>7</v>
       </c>
       <c r="AY18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BB18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC18" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="BF18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BG18" t="n">
         <v>1.17</v>
@@ -4456,28 +4456,28 @@
         <v>4</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="BJ18" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="BK18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BN18" t="n">
         <v>1.75</v>
       </c>
-      <c r="BL18" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>1.65</v>
-      </c>
       <c r="BO18" t="n">
-        <v>2.66</v>
+        <v>2.95</v>
       </c>
       <c r="BP18" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="19">
@@ -4703,7 +4703,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>8125649</v>
+        <v>7962668</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -4723,110 +4723,110 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M20" t="n">
         <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>['74']</t>
+          <t>['11', '31', '90+6']</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>['33']</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>2.25</v>
+        <v>3.65</v>
       </c>
       <c r="R20" t="n">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="S20" t="n">
-        <v>4.41</v>
+        <v>2.4</v>
       </c>
       <c r="T20" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="U20" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="V20" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="W20" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="X20" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y20" t="n">
         <v>1.13</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.72</v>
+        <v>3.51</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.63</v>
+        <v>3.74</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC20" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AD20" t="n">
         <v>13</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF20" t="n">
-        <v>4.33</v>
+        <v>4.55</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.15</v>
+        <v>2.48</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.23</v>
+        <v>2.62</v>
       </c>
       <c r="AK20" t="n">
         <v>1.25</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AM20" t="n">
-        <v>2.05</v>
+        <v>1.33</v>
       </c>
       <c r="AN20" t="n">
         <v>0</v>
@@ -4835,55 +4835,55 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.33</v>
+        <v>2.17</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.33</v>
+        <v>1.43</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.59</v>
+        <v>1.19</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.88</v>
+        <v>1.95</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.47</v>
+        <v>3.14</v>
       </c>
       <c r="AU20" t="n">
         <v>7</v>
       </c>
       <c r="AV20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX20" t="n">
         <v>7</v>
       </c>
       <c r="AY20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA20" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BB20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC20" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BG20" t="n">
         <v>1.17</v>
@@ -4892,28 +4892,28 @@
         <v>4</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="BJ20" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="BL20" t="n">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="BM20" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="BO20" t="n">
-        <v>2.95</v>
+        <v>2.66</v>
       </c>
       <c r="BP20" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="21">
@@ -5575,7 +5575,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>7962669</v>
+        <v>7962670</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -5595,12 +5595,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -5616,176 +5616,176 @@
         <v>1</v>
       </c>
       <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>['50']</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>['84']</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="V24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AN24" t="n">
         <v>3</v>
       </c>
-      <c r="N24" t="n">
+      <c r="AO24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV24" t="n">
         <v>4</v>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>['89']</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>['72', '80', '90+5']</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="R24" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="U24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V24" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X24" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>8</v>
-      </c>
       <c r="AW24" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AX24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AZ24" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA24" t="n">
         <v>5</v>
       </c>
       <c r="BB24" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="BC24" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="BD24" t="n">
-        <v>2.13</v>
+        <v>1.68</v>
       </c>
       <c r="BE24" t="n">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.94</v>
+        <v>2.75</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="BH24" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
       <c r="BJ24" t="n">
-        <v>2.84</v>
+        <v>2.45</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.63</v>
+        <v>2.19</v>
       </c>
       <c r="BL24" t="n">
-        <v>2.16</v>
+        <v>1.9</v>
       </c>
       <c r="BM24" t="n">
-        <v>2.03</v>
+        <v>2.36</v>
       </c>
       <c r="BN24" t="n">
-        <v>1.74</v>
+        <v>1.52</v>
       </c>
       <c r="BO24" t="n">
-        <v>2.59</v>
+        <v>3.14</v>
       </c>
       <c r="BP24" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="25">
@@ -5793,7 +5793,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>7962670</v>
+        <v>7962669</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -5813,12 +5813,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -5834,176 +5834,176 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
+        <v>4</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>['72', '80', '90+5']</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V25" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO25" t="n">
         <v>2</v>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>['50']</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>['84']</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R25" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="S25" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="U25" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="V25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X25" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AP25" t="n">
-        <v>2.17</v>
+        <v>0.83</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.33</v>
+        <v>1.17</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.52</v>
+        <v>1.08</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.65</v>
+        <v>2.32</v>
       </c>
       <c r="AU25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AV25" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AW25" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AX25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AZ25" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BA25" t="n">
         <v>5</v>
       </c>
       <c r="BB25" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="BC25" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.68</v>
+        <v>2.13</v>
       </c>
       <c r="BE25" t="n">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BF25" t="n">
-        <v>2.75</v>
+        <v>1.94</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="BH25" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="BI25" t="n">
-        <v>1.56</v>
+        <v>1.39</v>
       </c>
       <c r="BJ25" t="n">
-        <v>2.45</v>
+        <v>2.84</v>
       </c>
       <c r="BK25" t="n">
-        <v>2.19</v>
+        <v>1.63</v>
       </c>
       <c r="BL25" t="n">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="BM25" t="n">
-        <v>2.36</v>
+        <v>2.03</v>
       </c>
       <c r="BN25" t="n">
-        <v>1.52</v>
+        <v>1.74</v>
       </c>
       <c r="BO25" t="n">
-        <v>3.14</v>
+        <v>2.59</v>
       </c>
       <c r="BP25" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="26">
@@ -8191,7 +8191,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>7962659</v>
+        <v>7962663</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -8211,110 +8211,110 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N36" t="n">
         <v>2</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>['59', '67']</t>
+          <t>['51']</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="R36" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S36" t="n">
-        <v>3.16</v>
+        <v>4.33</v>
       </c>
       <c r="T36" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="U36" t="n">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="V36" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="W36" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="X36" t="n">
         <v>5.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z36" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH36" t="n">
         <v>2.15</v>
       </c>
-      <c r="AA36" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>2.11</v>
-      </c>
       <c r="AI36" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AJ36" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="AK36" t="n">
         <v>1.25</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.5</v>
+        <v>1.96</v>
       </c>
       <c r="AN36" t="n">
         <v>1.5</v>
@@ -8323,37 +8323,37 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.17</v>
+        <v>2.17</v>
       </c>
       <c r="AQ36" t="n">
         <v>1</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.2</v>
+        <v>1.46</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.58</v>
+        <v>1.34</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AU36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW36" t="n">
         <v>6</v>
       </c>
       <c r="AX36" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY36" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AZ36" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA36" t="n">
         <v>4</v>
@@ -8365,43 +8365,43 @@
         <v>11</v>
       </c>
       <c r="BD36" t="n">
-        <v>2.28</v>
+        <v>1.7</v>
       </c>
       <c r="BE36" t="n">
-        <v>6.65</v>
+        <v>8.5</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.93</v>
+        <v>2.44</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="BH36" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="BI36" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="BJ36" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="BK36" t="n">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="BL36" t="n">
-        <v>2.34</v>
+        <v>2.05</v>
       </c>
       <c r="BM36" t="n">
-        <v>1.88</v>
+        <v>2.14</v>
       </c>
       <c r="BN36" t="n">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="BO36" t="n">
-        <v>2.39</v>
+        <v>2.68</v>
       </c>
       <c r="BP36" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="37">
@@ -8409,7 +8409,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>7962663</v>
+        <v>7962659</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -8429,110 +8429,110 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N37" t="n">
         <v>2</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>['13']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>['51']</t>
+          <t>['59', '67']</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="R37" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S37" t="n">
-        <v>4.33</v>
+        <v>3.16</v>
       </c>
       <c r="T37" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="U37" t="n">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="V37" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="W37" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="X37" t="n">
         <v>5.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.5</v>
+        <v>3.63</v>
       </c>
       <c r="AB37" t="n">
-        <v>3.86</v>
+        <v>2.8</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AD37" t="n">
-        <v>13</v>
+        <v>13.4</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF37" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AJ37" t="n">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="AK37" t="n">
         <v>1.25</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.96</v>
+        <v>1.5</v>
       </c>
       <c r="AN37" t="n">
         <v>1.5</v>
@@ -8541,37 +8541,37 @@
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>2.17</v>
+        <v>1.17</v>
       </c>
       <c r="AQ37" t="n">
         <v>1</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.46</v>
+        <v>1.2</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.34</v>
+        <v>1.58</v>
       </c>
       <c r="AT37" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="AU37" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AV37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW37" t="n">
         <v>6</v>
       </c>
       <c r="AX37" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY37" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ37" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA37" t="n">
         <v>4</v>
@@ -8583,43 +8583,43 @@
         <v>11</v>
       </c>
       <c r="BD37" t="n">
-        <v>1.7</v>
+        <v>2.28</v>
       </c>
       <c r="BE37" t="n">
-        <v>8.5</v>
+        <v>6.65</v>
       </c>
       <c r="BF37" t="n">
-        <v>2.44</v>
+        <v>1.93</v>
       </c>
       <c r="BG37" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="BH37" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="BI37" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="BJ37" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="BK37" t="n">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="BL37" t="n">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="BM37" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="BN37" t="n">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="BO37" t="n">
-        <v>2.68</v>
+        <v>2.39</v>
       </c>
       <c r="BP37" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="38">
@@ -11243,7 +11243,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>7962713</v>
+        <v>7962703</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -11263,19 +11263,19 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" t="n">
         <v>3</v>
@@ -11284,176 +11284,176 @@
         <v>3</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>['4', '30', '33']</t>
+          <t>['7', '18', '90+3']</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['6']</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>1.6</v>
+        <v>2.95</v>
       </c>
       <c r="R50" t="n">
-        <v>2.95</v>
+        <v>2.33</v>
       </c>
       <c r="S50" t="n">
-        <v>6.5</v>
+        <v>3.35</v>
       </c>
       <c r="T50" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="U50" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="V50" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="W50" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="X50" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.23</v>
+        <v>2.12</v>
       </c>
       <c r="AA50" t="n">
-        <v>5.8</v>
+        <v>3.51</v>
       </c>
       <c r="AB50" t="n">
-        <v>7.4</v>
+        <v>2.76</v>
       </c>
       <c r="AC50" t="n">
         <v>1.01</v>
       </c>
       <c r="AD50" t="n">
-        <v>26</v>
+        <v>18.5</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF50" t="n">
-        <v>6.75</v>
+        <v>4.9</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AH50" t="n">
-        <v>3.4</v>
+        <v>2.48</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AJ50" t="n">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="AL50" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AM50" t="n">
-        <v>3.5</v>
+        <v>1.66</v>
       </c>
       <c r="AN50" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AO50" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="AP50" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.17</v>
+        <v>1</v>
       </c>
       <c r="AR50" t="n">
-        <v>2.4</v>
+        <v>1.87</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AT50" t="n">
-        <v>3.89</v>
+        <v>3.38</v>
       </c>
       <c r="AU50" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW50" t="n">
         <v>9</v>
       </c>
-      <c r="AV50" t="n">
+      <c r="AX50" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA50" t="n">
         <v>4</v>
       </c>
-      <c r="AW50" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>30</v>
-      </c>
-      <c r="AZ50" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA50" t="n">
-        <v>10</v>
-      </c>
       <c r="BB50" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BC50" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BD50" t="n">
-        <v>1.19</v>
+        <v>1.91</v>
       </c>
       <c r="BE50" t="n">
-        <v>13</v>
+        <v>8.5</v>
       </c>
       <c r="BF50" t="n">
-        <v>5.7</v>
+        <v>2.12</v>
       </c>
       <c r="BG50" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="BH50" t="n">
-        <v>4.15</v>
+        <v>3.7</v>
       </c>
       <c r="BI50" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="BJ50" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="BK50" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="BL50" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="BM50" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="BN50" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="BO50" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="BP50" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="51">
@@ -11461,7 +11461,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>7962703</v>
+        <v>7962713</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -11481,19 +11481,19 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
         <v>3</v>
@@ -11502,176 +11502,176 @@
         <v>3</v>
       </c>
       <c r="M51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>['7', '18', '90+3']</t>
+          <t>['4', '30', '33']</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>['6']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q51" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R51" t="n">
         <v>2.95</v>
       </c>
-      <c r="R51" t="n">
-        <v>2.33</v>
-      </c>
       <c r="S51" t="n">
-        <v>3.35</v>
+        <v>6.5</v>
       </c>
       <c r="T51" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="U51" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="V51" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="W51" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="X51" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.12</v>
+        <v>1.23</v>
       </c>
       <c r="AA51" t="n">
-        <v>3.51</v>
+        <v>5.8</v>
       </c>
       <c r="AB51" t="n">
-        <v>2.76</v>
+        <v>7.4</v>
       </c>
       <c r="AC51" t="n">
         <v>1.01</v>
       </c>
       <c r="AD51" t="n">
-        <v>18.5</v>
+        <v>26</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF51" t="n">
-        <v>4.9</v>
+        <v>6.75</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AH51" t="n">
-        <v>2.48</v>
+        <v>3.4</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AJ51" t="n">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AL51" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AM51" t="n">
-        <v>1.66</v>
+        <v>3.5</v>
       </c>
       <c r="AN51" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AO51" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="AP51" t="n">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1</v>
+        <v>0.17</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
       <c r="AS51" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AT51" t="n">
-        <v>3.38</v>
+        <v>3.89</v>
       </c>
       <c r="AU51" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>30</v>
+      </c>
+      <c r="AZ51" t="n">
         <v>8</v>
       </c>
-      <c r="AV51" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>17</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>17</v>
-      </c>
       <c r="BA51" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="BB51" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BC51" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BD51" t="n">
-        <v>1.91</v>
+        <v>1.19</v>
       </c>
       <c r="BE51" t="n">
-        <v>8.5</v>
+        <v>13</v>
       </c>
       <c r="BF51" t="n">
-        <v>2.12</v>
+        <v>5.7</v>
       </c>
       <c r="BG51" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="BH51" t="n">
-        <v>3.7</v>
+        <v>4.15</v>
       </c>
       <c r="BI51" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="BJ51" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="BK51" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="BL51" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="BM51" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="BN51" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="BO51" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="BP51" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="52">
@@ -12551,7 +12551,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>7962718</v>
+        <v>7962719</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -12571,197 +12571,197 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
+          <t>['10', '15', '29', '72', '90+2']</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>['12']</t>
-        </is>
-      </c>
       <c r="Q56" t="n">
-        <v>2.79</v>
+        <v>2.25</v>
       </c>
       <c r="R56" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="S56" t="n">
-        <v>3.64</v>
+        <v>4.52</v>
       </c>
       <c r="T56" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="U56" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="V56" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="W56" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="X56" t="n">
-        <v>5.75</v>
+        <v>4.8</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.27</v>
+        <v>1.73</v>
       </c>
       <c r="AA56" t="n">
-        <v>3.46</v>
+        <v>3.6</v>
       </c>
       <c r="AB56" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AD56" t="n">
         <v>10</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF56" t="n">
-        <v>4.72</v>
+        <v>4.5</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AH56" t="n">
-        <v>2.01</v>
+        <v>2.25</v>
       </c>
       <c r="AI56" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AJ56" t="n">
         <v>2.3</v>
       </c>
       <c r="AK56" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AL56" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AM56" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="AN56" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="AO56" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.17</v>
+        <v>2</v>
       </c>
       <c r="AQ56" t="n">
-        <v>2.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.38</v>
+        <v>1.87</v>
       </c>
       <c r="AS56" t="n">
-        <v>1.72</v>
+        <v>1.35</v>
       </c>
       <c r="AT56" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="AU56" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AV56" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AW56" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AX56" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AY56" t="n">
         <v>17</v>
       </c>
       <c r="AZ56" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="BA56" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BB56" t="n">
         <v>3</v>
       </c>
       <c r="BC56" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BD56" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="BE56" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="BF56" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="BG56" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="BH56" t="n">
-        <v>2.85</v>
+        <v>3.75</v>
       </c>
       <c r="BI56" t="n">
-        <v>1.65</v>
+        <v>1.41</v>
       </c>
       <c r="BJ56" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK56" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BL56" t="n">
         <v>2.16</v>
       </c>
-      <c r="BK56" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BL56" t="n">
-        <v>1.76</v>
-      </c>
       <c r="BM56" t="n">
-        <v>2.5</v>
+        <v>1.94</v>
       </c>
       <c r="BN56" t="n">
-        <v>1.45</v>
+        <v>1.73</v>
       </c>
       <c r="BO56" t="n">
-        <v>3.35</v>
+        <v>2.6</v>
       </c>
       <c r="BP56" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="57">
@@ -12769,7 +12769,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>7962719</v>
+        <v>7962718</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -12789,197 +12789,197 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N57" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>['10', '15', '29', '72', '90+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['12']</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>2.25</v>
+        <v>2.79</v>
       </c>
       <c r="R57" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="S57" t="n">
-        <v>4.52</v>
+        <v>3.64</v>
       </c>
       <c r="T57" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="U57" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="V57" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="W57" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="X57" t="n">
-        <v>4.8</v>
+        <v>5.75</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.73</v>
+        <v>2.27</v>
       </c>
       <c r="AA57" t="n">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="AB57" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AD57" t="n">
         <v>10</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF57" t="n">
-        <v>4.5</v>
+        <v>4.72</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AH57" t="n">
-        <v>2.25</v>
+        <v>2.01</v>
       </c>
       <c r="AI57" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AJ57" t="n">
         <v>2.3</v>
       </c>
       <c r="AK57" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AL57" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AM57" t="n">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="AN57" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="AO57" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="AP57" t="n">
-        <v>2</v>
+        <v>1.17</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.33</v>
+        <v>2.5</v>
       </c>
       <c r="AR57" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="AS57" t="n">
-        <v>1.35</v>
+        <v>1.72</v>
       </c>
       <c r="AT57" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="AU57" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX57" t="n">
         <v>11</v>
-      </c>
-      <c r="AV57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW57" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX57" t="n">
-        <v>9</v>
       </c>
       <c r="AY57" t="n">
         <v>17</v>
       </c>
       <c r="AZ57" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="BA57" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BB57" t="n">
         <v>3</v>
       </c>
       <c r="BC57" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BD57" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="BE57" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="BF57" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="BG57" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="BH57" t="n">
-        <v>3.75</v>
+        <v>2.85</v>
       </c>
       <c r="BI57" t="n">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="BJ57" t="n">
-        <v>2.7</v>
+        <v>2.16</v>
       </c>
       <c r="BK57" t="n">
-        <v>1.61</v>
+        <v>1.97</v>
       </c>
       <c r="BL57" t="n">
-        <v>2.16</v>
+        <v>1.76</v>
       </c>
       <c r="BM57" t="n">
-        <v>1.94</v>
+        <v>2.5</v>
       </c>
       <c r="BN57" t="n">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
       <c r="BO57" t="n">
-        <v>2.6</v>
+        <v>3.35</v>
       </c>
       <c r="BP57" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="58">
@@ -15821,7 +15821,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>7962731</v>
+        <v>7962732</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -15841,197 +15841,197 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
+          <t>['18', '27', '40', '66', '71', '73']</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="Q71" t="n">
-        <v>3.15</v>
+        <v>2.38</v>
       </c>
       <c r="R71" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="S71" t="n">
-        <v>2.91</v>
+        <v>3.75</v>
       </c>
       <c r="T71" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="U71" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="V71" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="W71" t="n">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="X71" t="n">
-        <v>3.65</v>
+        <v>5.2</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="Z71" t="n">
-        <v>2.65</v>
+        <v>1.79</v>
       </c>
       <c r="AA71" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AB71" t="n">
-        <v>2.51</v>
+        <v>3.9</v>
       </c>
       <c r="AC71" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AD71" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF71" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="AG71" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AH71" t="n">
-        <v>3.05</v>
+        <v>2.2</v>
       </c>
       <c r="AI71" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AJ71" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK71" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AP71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ71" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AR71" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS71" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AT71" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AU71" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV71" t="n">
         <v>3</v>
       </c>
-      <c r="AK71" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AL71" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AM71" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN71" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO71" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AP71" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AQ71" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR71" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AS71" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AT71" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AU71" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV71" t="n">
-        <v>0</v>
-      </c>
       <c r="AW71" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX71" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AY71" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AZ71" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA71" t="n">
         <v>3</v>
       </c>
       <c r="BB71" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BC71" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BD71" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="BE71" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF71" t="n">
-        <v>2.14</v>
+        <v>3</v>
       </c>
       <c r="BG71" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="BH71" t="n">
-        <v>4.55</v>
+        <v>3.78</v>
       </c>
       <c r="BI71" t="n">
         <v>1.4</v>
       </c>
       <c r="BJ71" t="n">
-        <v>2.87</v>
+        <v>2.63</v>
       </c>
       <c r="BK71" t="n">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="BL71" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="BM71" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="BN71" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="BO71" t="n">
         <v>2.63</v>
       </c>
       <c r="BP71" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="72">
@@ -16039,7 +16039,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>7962732</v>
+        <v>7962731</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -16059,197 +16059,197 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R72" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S72" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U72" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V72" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W72" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="X72" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AJ72" t="n">
         <v>3</v>
       </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
-        <v>3</v>
-      </c>
-      <c r="L72" t="n">
+      <c r="AK72" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO72" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP72" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AQ72" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR72" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS72" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AT72" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AU72" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW72" t="n">
         <v>6</v>
       </c>
-      <c r="M72" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" t="n">
-        <v>6</v>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>['18', '27', '40', '66', '71', '73']</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q72" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R72" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="S72" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T72" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="U72" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V72" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="W72" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X72" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="Y72" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z72" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AA72" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB72" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AC72" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AD72" t="n">
+      <c r="AX72" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY72" t="n">
         <v>10</v>
       </c>
-      <c r="AE72" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF72" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AG72" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH72" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AI72" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AJ72" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AK72" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AL72" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AM72" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AN72" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AO72" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AP72" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ72" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AR72" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AS72" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AT72" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AU72" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV72" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW72" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX72" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY72" t="n">
-        <v>14</v>
-      </c>
       <c r="AZ72" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA72" t="n">
         <v>3</v>
       </c>
       <c r="BB72" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BC72" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BD72" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="BE72" t="n">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="BF72" t="n">
-        <v>3</v>
+        <v>2.14</v>
       </c>
       <c r="BG72" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="BH72" t="n">
-        <v>3.78</v>
+        <v>4.55</v>
       </c>
       <c r="BI72" t="n">
         <v>1.4</v>
       </c>
       <c r="BJ72" t="n">
-        <v>2.63</v>
+        <v>2.87</v>
       </c>
       <c r="BK72" t="n">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="BL72" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="BM72" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="BN72" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="BO72" t="n">
         <v>2.63</v>
       </c>
       <c r="BP72" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP72"/>
+  <dimension ref="A1:BP75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ2" t="n">
         <v>1.83</v>
@@ -1350,7 +1350,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.33</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ9" t="n">
         <v>1.8</v>
@@ -2658,7 +2658,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
         <v>1</v>
       </c>
       <c r="AQ16" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AR16" t="n">
         <v>1.24</v>
@@ -4399,10 +4399,10 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AR18" t="n">
         <v>1.59</v>
@@ -5053,10 +5053,10 @@
         <v>3</v>
       </c>
       <c r="AP21" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ21" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AR21" t="n">
         <v>1.21</v>
@@ -5492,7 +5492,7 @@
         <v>2</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR23" t="n">
         <v>1.97</v>
@@ -5710,7 +5710,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AR24" t="n">
         <v>1.52</v>
@@ -5925,7 +5925,7 @@
         <v>2</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AQ25" t="n">
         <v>1.17</v>
@@ -6797,10 +6797,10 @@
         <v>3</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR29" t="n">
         <v>1.79</v>
@@ -7233,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ31" t="n">
         <v>1</v>
@@ -7669,7 +7669,7 @@
         <v>2</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AQ33" t="n">
         <v>1.83</v>
@@ -8759,7 +8759,7 @@
         <v>0.33</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ38" t="n">
         <v>0.17</v>
@@ -8980,7 +8980,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AR39" t="n">
         <v>1.4</v>
@@ -9195,7 +9195,7 @@
         <v>3</v>
       </c>
       <c r="AP40" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ40" t="n">
         <v>1.8</v>
@@ -9416,7 +9416,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ41" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AR41" t="n">
         <v>1.93</v>
@@ -9852,7 +9852,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR43" t="n">
         <v>2.38</v>
@@ -10288,7 +10288,7 @@
         <v>2</v>
       </c>
       <c r="AQ45" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AR45" t="n">
         <v>1.92</v>
@@ -10939,7 +10939,7 @@
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AQ48" t="n">
         <v>0.6</v>
@@ -11157,7 +11157,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ49" t="n">
         <v>1.43</v>
@@ -12686,7 +12686,7 @@
         <v>2</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AR56" t="n">
         <v>1.87</v>
@@ -12904,7 +12904,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ57" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AR57" t="n">
         <v>1.38</v>
@@ -13119,10 +13119,10 @@
         <v>2.5</v>
       </c>
       <c r="AP58" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR58" t="n">
         <v>1.1</v>
@@ -13337,7 +13337,7 @@
         <v>1</v>
       </c>
       <c r="AP59" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ59" t="n">
         <v>1.33</v>
@@ -13773,7 +13773,7 @@
         <v>0.75</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ61" t="n">
         <v>0.6</v>
@@ -14866,7 +14866,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AR66" t="n">
         <v>1.4</v>
@@ -15299,7 +15299,7 @@
         <v>1.2</v>
       </c>
       <c r="AP68" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AQ68" t="n">
         <v>1</v>
@@ -15735,7 +15735,7 @@
         <v>0.6</v>
       </c>
       <c r="AP70" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ70" t="n">
         <v>1</v>
@@ -15956,7 +15956,7 @@
         <v>1</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AR71" t="n">
         <v>1.41</v>
@@ -16250,6 +16250,660 @@
       </c>
       <c r="BP72" t="n">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="n">
+        <v>7962735</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>45969.58333333334</v>
+      </c>
+      <c r="F73" t="n">
+        <v>13</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Winterthur</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1</v>
+      </c>
+      <c r="N73" t="n">
+        <v>1</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>['90+2']</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R73" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S73" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U73" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V73" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="W73" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X73" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ73" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AK73" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AO73" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AP73" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AQ73" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AR73" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AS73" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AT73" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AU73" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV73" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW73" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX73" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY73" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ73" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA73" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB73" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC73" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD73" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BE73" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="BF73" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BG73" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH73" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BI73" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ73" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BK73" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL73" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM73" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BN73" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BO73" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP73" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="n">
+        <v>7962736</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>45969.58333333334</v>
+      </c>
+      <c r="F74" t="n">
+        <v>13</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Zürich</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Luzern</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>2</v>
+      </c>
+      <c r="K74" t="n">
+        <v>2</v>
+      </c>
+      <c r="L74" t="n">
+        <v>3</v>
+      </c>
+      <c r="M74" t="n">
+        <v>2</v>
+      </c>
+      <c r="N74" t="n">
+        <v>5</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>['75', '79', '90+2']</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>['2', '43']</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R74" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S74" t="n">
+        <v>3</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U74" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V74" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W74" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X74" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ74" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK74" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO74" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AP74" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ74" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR74" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AS74" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AT74" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU74" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV74" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW74" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX74" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY74" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ74" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA74" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB74" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC74" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD74" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BE74" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF74" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BG74" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH74" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI74" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ74" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BK74" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BL74" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BM74" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN74" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BO74" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BP74" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="n">
+        <v>7962737</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>45969.6875</v>
+      </c>
+      <c r="F75" t="n">
+        <v>13</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Servette</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Thun</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1</v>
+      </c>
+      <c r="N75" t="n">
+        <v>1</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>['90']</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R75" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S75" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U75" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V75" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X75" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AJ75" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AK75" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO75" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AP75" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ75" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AR75" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS75" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AT75" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AU75" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV75" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW75" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX75" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY75" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ75" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA75" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB75" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC75" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD75" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BE75" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF75" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BG75" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH75" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI75" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ75" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BK75" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BL75" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM75" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BN75" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO75" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BP75" t="n">
+        <v>1.45</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP75"/>
+  <dimension ref="A1:BP78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.43</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AQ6" t="n">
         <v>0.17</v>
@@ -2222,7 +2222,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AQ10" t="n">
         <v>0.71</v>
@@ -3094,7 +3094,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3527,10 +3527,10 @@
         <v>1</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AR14" t="n">
         <v>2.11</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ15" t="n">
         <v>0.17</v>
@@ -4184,7 +4184,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AR17" t="n">
         <v>2.37</v>
@@ -4617,7 +4617,7 @@
         <v>1</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AQ19" t="n">
         <v>1.17</v>
@@ -5489,7 +5489,7 @@
         <v>3</v>
       </c>
       <c r="AP23" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ23" t="n">
         <v>1.57</v>
@@ -6361,7 +6361,7 @@
         <v>3</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.8</v>
@@ -6582,7 +6582,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AR28" t="n">
         <v>1.93</v>
@@ -7451,10 +7451,10 @@
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AR32" t="n">
         <v>2.08</v>
@@ -7672,7 +7672,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AR33" t="n">
         <v>1.07</v>
@@ -7890,7 +7890,7 @@
         <v>1</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AR34" t="n">
         <v>1.27</v>
@@ -9849,7 +9849,7 @@
         <v>2.33</v>
       </c>
       <c r="AP43" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AQ43" t="n">
         <v>1.57</v>
@@ -10070,7 +10070,7 @@
         <v>1</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AR44" t="n">
         <v>1.24</v>
@@ -10285,7 +10285,7 @@
         <v>2.25</v>
       </c>
       <c r="AP45" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ45" t="n">
         <v>2.57</v>
@@ -10721,10 +10721,10 @@
         <v>1.33</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AR47" t="n">
         <v>1.67</v>
@@ -10942,7 +10942,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AR48" t="n">
         <v>1.09</v>
@@ -11593,7 +11593,7 @@
         <v>0.25</v>
       </c>
       <c r="AP51" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AQ51" t="n">
         <v>0.17</v>
@@ -12032,7 +12032,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AR53" t="n">
         <v>1.56</v>
@@ -12683,7 +12683,7 @@
         <v>0.5</v>
       </c>
       <c r="AP56" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ56" t="n">
         <v>0.71</v>
@@ -13340,7 +13340,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AR59" t="n">
         <v>1.96</v>
@@ -13555,7 +13555,7 @@
         <v>1.8</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AQ60" t="n">
         <v>1.43</v>
@@ -13776,7 +13776,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AR61" t="n">
         <v>1.88</v>
@@ -14427,7 +14427,7 @@
         <v>0.75</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AQ64" t="n">
         <v>1</v>
@@ -14645,7 +14645,7 @@
         <v>1.4</v>
       </c>
       <c r="AP65" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AQ65" t="n">
         <v>1.17</v>
@@ -15084,7 +15084,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AR67" t="n">
         <v>1.44</v>
@@ -15520,7 +15520,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AR69" t="n">
         <v>1.94</v>
@@ -16904,6 +16904,660 @@
       </c>
       <c r="BP75" t="n">
         <v>1.45</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="n">
+        <v>7962740</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>45970.41666666666</v>
+      </c>
+      <c r="F76" t="n">
+        <v>13</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Basel</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Lugano</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1</v>
+      </c>
+      <c r="N76" t="n">
+        <v>1</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>['62']</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="R76" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S76" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="U76" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V76" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="W76" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="X76" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK76" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL76" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AP76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR76" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AS76" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AT76" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="AU76" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV76" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW76" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX76" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY76" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ76" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA76" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB76" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC76" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD76" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BE76" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF76" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BG76" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH76" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI76" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ76" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BK76" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL76" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BM76" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BN76" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BO76" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="BP76" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="n">
+        <v>7962738</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>45970.52083333334</v>
+      </c>
+      <c r="F77" t="n">
+        <v>13</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Lausanne Sport</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Sion</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>2</v>
+      </c>
+      <c r="J77" t="n">
+        <v>2</v>
+      </c>
+      <c r="K77" t="n">
+        <v>4</v>
+      </c>
+      <c r="L77" t="n">
+        <v>2</v>
+      </c>
+      <c r="M77" t="n">
+        <v>2</v>
+      </c>
+      <c r="N77" t="n">
+        <v>4</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>['20', '33']</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>['7', '11']</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R77" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S77" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T77" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U77" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="V77" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="W77" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X77" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AI77" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AJ77" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AK77" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL77" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AP77" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ77" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AR77" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AS77" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AT77" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AU77" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV77" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW77" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX77" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY77" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ77" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA77" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB77" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC77" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD77" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BE77" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="BF77" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BG77" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BH77" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="BI77" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BJ77" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="BK77" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BL77" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BM77" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BN77" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BO77" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BP77" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="n">
+        <v>7962739</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>45970.52083333334</v>
+      </c>
+      <c r="F78" t="n">
+        <v>13</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>St. Gallen</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Young Boys</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" t="n">
+        <v>2</v>
+      </c>
+      <c r="K78" t="n">
+        <v>3</v>
+      </c>
+      <c r="L78" t="n">
+        <v>1</v>
+      </c>
+      <c r="M78" t="n">
+        <v>4</v>
+      </c>
+      <c r="N78" t="n">
+        <v>5</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>['9']</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>['7', '32', '51', '64']</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R78" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="S78" t="n">
+        <v>3</v>
+      </c>
+      <c r="T78" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U78" t="n">
+        <v>4</v>
+      </c>
+      <c r="V78" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W78" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X78" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AJ78" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AK78" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL78" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP78" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AQ78" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR78" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AS78" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AT78" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AU78" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV78" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW78" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX78" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY78" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ78" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA78" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB78" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC78" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD78" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BE78" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF78" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BG78" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BH78" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="BI78" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ78" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BK78" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BL78" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BM78" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BN78" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BO78" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BP78" t="n">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -17297,10 +17297,10 @@
         <v>4</v>
       </c>
       <c r="BB77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC77" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD77" t="n">
         <v>1.56</v>
@@ -17500,13 +17500,13 @@
         <v>6</v>
       </c>
       <c r="AW78" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX78" t="n">
         <v>7</v>
       </c>
       <c r="AY78" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ78" t="n">
         <v>13</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP78"/>
+  <dimension ref="A1:BP84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ4" t="n">
         <v>1.57</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ5" t="n">
         <v>1</v>
@@ -1786,7 +1786,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3091,10 +3091,10 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>1</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3745,10 +3745,10 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR15" t="n">
         <v>2.05</v>
@@ -4181,7 +4181,7 @@
         <v>3</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ17" t="n">
         <v>1.71</v>
@@ -4620,7 +4620,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR19" t="n">
         <v>2.5</v>
@@ -4838,7 +4838,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR20" t="n">
         <v>1.19</v>
@@ -5271,10 +5271,10 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR22" t="n">
         <v>1.7</v>
@@ -5489,7 +5489,7 @@
         <v>3</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ23" t="n">
         <v>1.57</v>
@@ -5707,7 +5707,7 @@
         <v>0.5</v>
       </c>
       <c r="AP24" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ24" t="n">
         <v>0.71</v>
@@ -5928,7 +5928,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR25" t="n">
         <v>1.08</v>
@@ -6143,10 +6143,10 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR26" t="n">
         <v>1.52</v>
@@ -6579,10 +6579,10 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR28" t="n">
         <v>1.93</v>
@@ -7015,10 +7015,10 @@
         <v>1</v>
       </c>
       <c r="AP30" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR30" t="n">
         <v>1.78</v>
@@ -7451,10 +7451,10 @@
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR32" t="n">
         <v>2.08</v>
@@ -8105,10 +8105,10 @@
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR35" t="n">
         <v>1.67</v>
@@ -8326,7 +8326,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR36" t="n">
         <v>1.46</v>
@@ -8541,7 +8541,7 @@
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AQ37" t="n">
         <v>1</v>
@@ -8762,7 +8762,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR38" t="n">
         <v>1.89</v>
@@ -9413,7 +9413,7 @@
         <v>3</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ41" t="n">
         <v>2.57</v>
@@ -9631,10 +9631,10 @@
         <v>0.33</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR42" t="n">
         <v>1.11</v>
@@ -10285,7 +10285,7 @@
         <v>2.25</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ45" t="n">
         <v>2.57</v>
@@ -10503,10 +10503,10 @@
         <v>2.33</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR46" t="n">
         <v>1.62</v>
@@ -10942,7 +10942,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR48" t="n">
         <v>1.09</v>
@@ -11160,7 +11160,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR49" t="n">
         <v>1.81</v>
@@ -11375,7 +11375,7 @@
         <v>1</v>
       </c>
       <c r="AP50" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ50" t="n">
         <v>1</v>
@@ -11596,7 +11596,7 @@
         <v>2</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR51" t="n">
         <v>2.4</v>
@@ -11814,7 +11814,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR52" t="n">
         <v>1.37</v>
@@ -12029,7 +12029,7 @@
         <v>2</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ53" t="n">
         <v>1.71</v>
@@ -12250,7 +12250,7 @@
         <v>1</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR54" t="n">
         <v>1.29</v>
@@ -12465,7 +12465,7 @@
         <v>2</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ55" t="n">
         <v>1.8</v>
@@ -12683,7 +12683,7 @@
         <v>0.5</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ56" t="n">
         <v>0.71</v>
@@ -12901,7 +12901,7 @@
         <v>2.4</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AQ57" t="n">
         <v>2.57</v>
@@ -13558,7 +13558,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR60" t="n">
         <v>1.75</v>
@@ -13776,7 +13776,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR61" t="n">
         <v>1.88</v>
@@ -13991,7 +13991,7 @@
         <v>2.25</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AQ62" t="n">
         <v>1.8</v>
@@ -14209,10 +14209,10 @@
         <v>0.2</v>
       </c>
       <c r="AP63" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR63" t="n">
         <v>1.87</v>
@@ -14648,7 +14648,7 @@
         <v>2</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR65" t="n">
         <v>2.48</v>
@@ -15081,7 +15081,7 @@
         <v>1.4</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ67" t="n">
         <v>1.57</v>
@@ -15517,7 +15517,7 @@
         <v>2.2</v>
       </c>
       <c r="AP69" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ69" t="n">
         <v>1.71</v>
@@ -15738,7 +15738,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR70" t="n">
         <v>1.96</v>
@@ -16171,10 +16171,10 @@
         <v>1.5</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR72" t="n">
         <v>1.74</v>
@@ -17046,7 +17046,7 @@
         <v>2</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR76" t="n">
         <v>2.3</v>
@@ -17479,7 +17479,7 @@
         <v>1.33</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ78" t="n">
         <v>1.57</v>
@@ -17558,6 +17558,1314 @@
       </c>
       <c r="BP78" t="n">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="n">
+        <v>7962741</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>45983.58333333334</v>
+      </c>
+      <c r="F79" t="n">
+        <v>14</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Luzern</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Servette</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>2</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>2</v>
+      </c>
+      <c r="L79" t="n">
+        <v>2</v>
+      </c>
+      <c r="M79" t="n">
+        <v>2</v>
+      </c>
+      <c r="N79" t="n">
+        <v>4</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>['2', '9']</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>['57', '72']</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="R79" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S79" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T79" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="U79" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V79" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W79" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X79" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR79" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AS79" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AT79" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AU79" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW79" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX79" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY79" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ79" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA79" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB79" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC79" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE79" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="BF79" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BG79" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH79" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI79" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ79" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BK79" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BL79" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BM79" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BN79" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BO79" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BP79" t="n">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="n">
+        <v>7962762</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>45983.58333333334</v>
+      </c>
+      <c r="F80" t="n">
+        <v>14</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Young Boys</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Winterthur</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>4</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>4</v>
+      </c>
+      <c r="L80" t="n">
+        <v>5</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>5</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>['7', '21', '27', '29', '75']</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R80" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="T80" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U80" t="n">
+        <v>4</v>
+      </c>
+      <c r="V80" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="W80" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="X80" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AI80" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ80" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AK80" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AL80" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AM80" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AP80" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ80" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AR80" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AS80" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AT80" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AU80" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW80" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX80" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY80" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ80" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA80" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC80" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD80" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BE80" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF80" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG80" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH80" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI80" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ80" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BK80" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BL80" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BM80" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BN80" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BO80" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BP80" t="n">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="n">
+        <v>7962744</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>45983.6875</v>
+      </c>
+      <c r="F81" t="n">
+        <v>14</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Thun</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Lugano</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>1</v>
+      </c>
+      <c r="N81" t="n">
+        <v>1</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>['86']</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>3</v>
+      </c>
+      <c r="R81" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S81" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T81" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="U81" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V81" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="W81" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X81" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI81" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AJ81" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK81" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL81" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM81" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP81" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ81" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR81" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS81" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AT81" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AU81" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV81" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW81" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX81" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY81" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ81" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA81" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB81" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC81" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD81" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BE81" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="BF81" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BG81" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH81" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI81" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BJ81" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BK81" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BL81" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BM81" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BN81" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BO81" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BP81" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="n">
+        <v>7962743</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>45984.41666666666</v>
+      </c>
+      <c r="F82" t="n">
+        <v>14</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Sion</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Zürich</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>2</v>
+      </c>
+      <c r="J82" t="n">
+        <v>1</v>
+      </c>
+      <c r="K82" t="n">
+        <v>3</v>
+      </c>
+      <c r="L82" t="n">
+        <v>2</v>
+      </c>
+      <c r="M82" t="n">
+        <v>2</v>
+      </c>
+      <c r="N82" t="n">
+        <v>4</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>['12', '40']</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>['45', '49']</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="R82" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S82" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="T82" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U82" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="V82" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="W82" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X82" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI82" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL82" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP82" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ82" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR82" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AS82" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AT82" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AU82" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV82" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW82" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX82" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY82" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ82" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA82" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC82" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD82" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE82" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF82" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BG82" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH82" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI82" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ82" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK82" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BL82" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BM82" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BN82" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BO82" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BP82" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="n">
+        <v>7962742</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>45984.52083333334</v>
+      </c>
+      <c r="F83" t="n">
+        <v>14</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Basel</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>1</v>
+      </c>
+      <c r="J83" t="n">
+        <v>1</v>
+      </c>
+      <c r="K83" t="n">
+        <v>2</v>
+      </c>
+      <c r="L83" t="n">
+        <v>1</v>
+      </c>
+      <c r="M83" t="n">
+        <v>1</v>
+      </c>
+      <c r="N83" t="n">
+        <v>2</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>['13']</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>['33']</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R83" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S83" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T83" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U83" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="V83" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="W83" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X83" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI83" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AJ83" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AK83" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL83" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM83" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO83" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AP83" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ83" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR83" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS83" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AT83" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AU83" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV83" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW83" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX83" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY83" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ83" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA83" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB83" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC83" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD83" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BE83" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF83" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BG83" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH83" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="BI83" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ83" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BK83" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BL83" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BM83" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BN83" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BO83" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BP83" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="n">
+        <v>7962761</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>45984.52083333334</v>
+      </c>
+      <c r="F84" t="n">
+        <v>14</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>St. Gallen</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Lausanne Sport</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>1</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="n">
+        <v>1</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R84" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="S84" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T84" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U84" t="n">
+        <v>4</v>
+      </c>
+      <c r="V84" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="W84" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X84" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH84" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AI84" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ84" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK84" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AL84" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM84" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AO84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP84" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AQ84" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AR84" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS84" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AT84" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AU84" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV84" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW84" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX84" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY84" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ84" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA84" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB84" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC84" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD84" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BE84" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF84" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BG84" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH84" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI84" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BJ84" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BK84" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL84" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BM84" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BN84" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BO84" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BP84" t="n">
+        <v>1.45</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -18820,13 +18820,13 @@
         <v>15</v>
       </c>
       <c r="BA84" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB84" t="n">
         <v>10</v>
       </c>
       <c r="BC84" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD84" t="n">
         <v>1.77</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP84"/>
+  <dimension ref="A1:BP85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ7" t="n">
         <v>2.57</v>
@@ -2440,7 +2440,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ20" t="n">
         <v>1.38</v>
@@ -6364,7 +6364,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR27" t="n">
         <v>2</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ36" t="n">
         <v>0.86</v>
@@ -8977,7 +8977,7 @@
         <v>0.67</v>
       </c>
       <c r="AP39" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ39" t="n">
         <v>0.71</v>
@@ -9198,7 +9198,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR40" t="n">
         <v>1.62</v>
@@ -11811,7 +11811,7 @@
         <v>1.75</v>
       </c>
       <c r="AP52" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ52" t="n">
         <v>1.14</v>
@@ -12468,7 +12468,7 @@
         <v>2</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR55" t="n">
         <v>1.78</v>
@@ -13994,7 +13994,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR62" t="n">
         <v>1.47</v>
@@ -14863,7 +14863,7 @@
         <v>2.2</v>
       </c>
       <c r="AP66" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ66" t="n">
         <v>1.57</v>
@@ -18866,6 +18866,224 @@
       </c>
       <c r="BP84" t="n">
         <v>1.45</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="n">
+        <v>8362535</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>45987.625</v>
+      </c>
+      <c r="F85" t="n">
+        <v>12</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Lugano</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>St. Gallen</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>1</v>
+      </c>
+      <c r="J85" t="n">
+        <v>1</v>
+      </c>
+      <c r="K85" t="n">
+        <v>2</v>
+      </c>
+      <c r="L85" t="n">
+        <v>1</v>
+      </c>
+      <c r="M85" t="n">
+        <v>3</v>
+      </c>
+      <c r="N85" t="n">
+        <v>4</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>['33']</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>['42', '62', '90+5']</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R85" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="S85" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T85" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U85" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V85" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="W85" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X85" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH85" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AI85" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ85" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK85" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL85" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AO85" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP85" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR85" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AS85" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AT85" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AU85" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV85" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW85" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX85" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY85" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ85" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA85" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB85" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC85" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD85" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BE85" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF85" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BG85" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH85" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI85" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ85" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BK85" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BL85" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BM85" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BN85" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BO85" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BP85" t="n">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Switzerland Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP85"/>
+  <dimension ref="A1:BP91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1783,10 +1783,10 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.14</v>
+        <v>0.5</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2001,10 +2001,10 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2655,10 +2655,10 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ13" t="n">
         <v>1.14</v>
@@ -3527,10 +3527,10 @@
         <v>1</v>
       </c>
       <c r="AP14" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR14" t="n">
         <v>2.11</v>
@@ -3748,7 +3748,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.14</v>
+        <v>0.5</v>
       </c>
       <c r="AR15" t="n">
         <v>2.05</v>
@@ -3963,10 +3963,10 @@
         <v>3</v>
       </c>
       <c r="AP16" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ16" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AR16" t="n">
         <v>1.24</v>
@@ -4184,7 +4184,7 @@
         <v>2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AR17" t="n">
         <v>2.37</v>
@@ -4399,10 +4399,10 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR18" t="n">
         <v>1.59</v>
@@ -4617,7 +4617,7 @@
         <v>1</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ19" t="n">
         <v>1.14</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ20" t="n">
         <v>1.38</v>
@@ -5053,10 +5053,10 @@
         <v>3</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AR21" t="n">
         <v>1.21</v>
@@ -5274,7 +5274,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.14</v>
+        <v>0.5</v>
       </c>
       <c r="AR22" t="n">
         <v>1.7</v>
@@ -5710,7 +5710,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR24" t="n">
         <v>1.52</v>
@@ -6361,10 +6361,10 @@
         <v>3</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ27" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR27" t="n">
         <v>2</v>
@@ -6797,7 +6797,7 @@
         <v>3</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ29" t="n">
         <v>1.57</v>
@@ -7233,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ31" t="n">
         <v>1</v>
@@ -7672,7 +7672,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AR33" t="n">
         <v>1.07</v>
@@ -7887,10 +7887,10 @@
         <v>0.5</v>
       </c>
       <c r="AP34" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR34" t="n">
         <v>1.27</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ36" t="n">
         <v>0.86</v>
@@ -8759,10 +8759,10 @@
         <v>0.33</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.14</v>
+        <v>0.5</v>
       </c>
       <c r="AR38" t="n">
         <v>1.89</v>
@@ -8977,10 +8977,10 @@
         <v>0.67</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR39" t="n">
         <v>1.4</v>
@@ -9195,10 +9195,10 @@
         <v>3</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ40" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR40" t="n">
         <v>1.62</v>
@@ -9416,7 +9416,7 @@
         <v>2</v>
       </c>
       <c r="AQ41" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AR41" t="n">
         <v>1.93</v>
@@ -9849,7 +9849,7 @@
         <v>2.33</v>
       </c>
       <c r="AP43" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ43" t="n">
         <v>1.57</v>
@@ -10067,10 +10067,10 @@
         <v>2.33</v>
       </c>
       <c r="AP44" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AR44" t="n">
         <v>1.24</v>
@@ -10288,7 +10288,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ45" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AR45" t="n">
         <v>1.92</v>
@@ -10721,10 +10721,10 @@
         <v>1.33</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR47" t="n">
         <v>1.67</v>
@@ -11157,7 +11157,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ49" t="n">
         <v>1.38</v>
@@ -11593,10 +11593,10 @@
         <v>0.25</v>
       </c>
       <c r="AP51" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.14</v>
+        <v>0.5</v>
       </c>
       <c r="AR51" t="n">
         <v>2.4</v>
@@ -11811,7 +11811,7 @@
         <v>1.75</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ52" t="n">
         <v>1.14</v>
@@ -12032,7 +12032,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AR53" t="n">
         <v>1.56</v>
@@ -12247,7 +12247,7 @@
         <v>0.5</v>
       </c>
       <c r="AP54" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ54" t="n">
         <v>0.86</v>
@@ -12468,7 +12468,7 @@
         <v>2</v>
       </c>
       <c r="AQ55" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR55" t="n">
         <v>1.78</v>
@@ -12686,7 +12686,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR56" t="n">
         <v>1.87</v>
@@ -12904,7 +12904,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ57" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AR57" t="n">
         <v>1.38</v>
@@ -13337,10 +13337,10 @@
         <v>1</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR59" t="n">
         <v>1.96</v>
@@ -13555,7 +13555,7 @@
         <v>1.8</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ60" t="n">
         <v>1.38</v>
@@ -13773,7 +13773,7 @@
         <v>0.75</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ61" t="n">
         <v>1.29</v>
@@ -13994,7 +13994,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ62" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR62" t="n">
         <v>1.47</v>
@@ -14212,7 +14212,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0.14</v>
+        <v>0.5</v>
       </c>
       <c r="AR63" t="n">
         <v>1.87</v>
@@ -14427,7 +14427,7 @@
         <v>0.75</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ64" t="n">
         <v>1</v>
@@ -14645,7 +14645,7 @@
         <v>1.4</v>
       </c>
       <c r="AP65" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ65" t="n">
         <v>1.14</v>
@@ -14863,7 +14863,7 @@
         <v>2.2</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ66" t="n">
         <v>1.57</v>
@@ -15084,7 +15084,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR67" t="n">
         <v>1.44</v>
@@ -15520,7 +15520,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AR69" t="n">
         <v>1.94</v>
@@ -15735,7 +15735,7 @@
         <v>0.6</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ70" t="n">
         <v>0.86</v>
@@ -15953,10 +15953,10 @@
         <v>0.4</v>
       </c>
       <c r="AP71" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR71" t="n">
         <v>1.41</v>
@@ -16392,7 +16392,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ73" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR73" t="n">
         <v>1.12</v>
@@ -16607,7 +16607,7 @@
         <v>1.83</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ74" t="n">
         <v>1.57</v>
@@ -16825,10 +16825,10 @@
         <v>2.5</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ75" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AR75" t="n">
         <v>1.73</v>
@@ -17043,7 +17043,7 @@
         <v>0.6</v>
       </c>
       <c r="AP76" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ76" t="n">
         <v>1.29</v>
@@ -17261,10 +17261,10 @@
         <v>1.83</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AR77" t="n">
         <v>1.88</v>
@@ -17482,7 +17482,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR78" t="n">
         <v>1.93</v>
@@ -17697,7 +17697,7 @@
         <v>1</v>
       </c>
       <c r="AP79" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ79" t="n">
         <v>1</v>
@@ -17918,7 +17918,7 @@
         <v>2</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0.14</v>
+        <v>0.5</v>
       </c>
       <c r="AR80" t="n">
         <v>1.64</v>
@@ -19005,10 +19005,10 @@
         <v>1.8</v>
       </c>
       <c r="AP85" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ85" t="n">
         <v>1.86</v>
-      </c>
-      <c r="AQ85" t="n">
-        <v>2</v>
       </c>
       <c r="AR85" t="n">
         <v>1.33</v>
@@ -19084,6 +19084,1314 @@
       </c>
       <c r="BP85" t="n">
         <v>1.35</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="n">
+        <v>7962767</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>45990.58333333334</v>
+      </c>
+      <c r="F86" t="n">
+        <v>15</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Zürich</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>1</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1</v>
+      </c>
+      <c r="L86" t="n">
+        <v>1</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="n">
+        <v>1</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>['20']</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="R86" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="S86" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="T86" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="U86" t="n">
+        <v>3</v>
+      </c>
+      <c r="V86" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="W86" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X86" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD86" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG86" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH86" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI86" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ86" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AK86" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL86" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM86" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO86" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AP86" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ86" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AR86" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AS86" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AT86" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AU86" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV86" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW86" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX86" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY86" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ86" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA86" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB86" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC86" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD86" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BE86" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF86" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BG86" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH86" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI86" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ86" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BK86" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BL86" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BM86" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BN86" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BO86" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BP86" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="n">
+        <v>7962765</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>45990.58333333334</v>
+      </c>
+      <c r="F87" t="n">
+        <v>15</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Lugano</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sion</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" t="n">
+        <v>1</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1</v>
+      </c>
+      <c r="N87" t="n">
+        <v>2</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>['29']</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>['63']</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="R87" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="S87" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T87" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U87" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V87" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="W87" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X87" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD87" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AG87" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH87" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI87" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ87" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK87" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL87" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM87" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO87" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AP87" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ87" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR87" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AS87" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AT87" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AU87" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV87" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW87" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX87" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY87" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ87" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA87" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB87" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC87" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD87" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BE87" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF87" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BG87" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH87" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI87" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ87" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK87" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BL87" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BM87" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BN87" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO87" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BP87" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="n">
+        <v>7962763</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>45990.6875</v>
+      </c>
+      <c r="F88" t="n">
+        <v>15</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Luzern</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Winterthur</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>1</v>
+      </c>
+      <c r="J88" t="n">
+        <v>1</v>
+      </c>
+      <c r="K88" t="n">
+        <v>2</v>
+      </c>
+      <c r="L88" t="n">
+        <v>1</v>
+      </c>
+      <c r="M88" t="n">
+        <v>3</v>
+      </c>
+      <c r="N88" t="n">
+        <v>4</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>['45']</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>['39', '63', '69']</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R88" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="T88" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U88" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="V88" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W88" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="X88" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH88" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AI88" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AJ88" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK88" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AL88" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AM88" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO88" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AP88" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AQ88" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR88" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AS88" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AT88" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU88" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV88" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW88" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX88" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY88" t="n">
+        <v>26</v>
+      </c>
+      <c r="AZ88" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA88" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB88" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC88" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD88" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BE88" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF88" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="BG88" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH88" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI88" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BJ88" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BK88" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BL88" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM88" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BN88" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BO88" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BP88" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="n">
+        <v>7962764</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>45991.41666666666</v>
+      </c>
+      <c r="F89" t="n">
+        <v>15</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Servette</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Young Boys</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>2</v>
+      </c>
+      <c r="J89" t="n">
+        <v>2</v>
+      </c>
+      <c r="K89" t="n">
+        <v>4</v>
+      </c>
+      <c r="L89" t="n">
+        <v>4</v>
+      </c>
+      <c r="M89" t="n">
+        <v>4</v>
+      </c>
+      <c r="N89" t="n">
+        <v>8</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>['12', '33', '61', '84']</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>['26', '45+3', '57', '68']</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R89" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="S89" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="T89" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="U89" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V89" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W89" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X89" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH89" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AI89" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ89" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AK89" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL89" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM89" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AO89" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AP89" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ89" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR89" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AS89" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AT89" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AU89" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV89" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW89" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX89" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY89" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ89" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA89" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB89" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC89" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD89" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BE89" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF89" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BG89" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH89" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI89" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ89" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BK89" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BL89" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM89" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BN89" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BO89" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BP89" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="n">
+        <v>7962768</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>45991.52083333334</v>
+      </c>
+      <c r="F90" t="n">
+        <v>15</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Basel</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>St. Gallen</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R90" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S90" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T90" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U90" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="V90" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W90" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="X90" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA90" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AC90" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD90" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG90" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH90" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AI90" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AJ90" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AK90" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL90" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AM90" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO90" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP90" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ90" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AR90" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AS90" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AT90" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="AU90" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV90" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW90" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX90" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY90" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ90" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA90" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB90" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC90" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD90" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BE90" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF90" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BG90" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH90" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="BI90" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ90" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="BK90" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL90" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BM90" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BN90" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BO90" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BP90" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="n">
+        <v>7962766</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>45991.52083333334</v>
+      </c>
+      <c r="F91" t="n">
+        <v>15</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Lausanne Sport</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Thun</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>2</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>2</v>
+      </c>
+      <c r="L91" t="n">
+        <v>2</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1</v>
+      </c>
+      <c r="N91" t="n">
+        <v>3</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>['13', '16']</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>['67']</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R91" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S91" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T91" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="U91" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="V91" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W91" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X91" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD91" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF91" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AG91" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH91" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AI91" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AJ91" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK91" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AL91" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM91" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO91" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AP91" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AQ91" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AR91" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AS91" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT91" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AU91" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV91" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW91" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX91" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY91" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ91" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA91" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB91" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC91" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD91" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BE91" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF91" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BG91" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH91" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="BI91" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ91" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BK91" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BL91" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BM91" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BN91" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO91" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BP91" t="n">
+        <v>1.46</v>
       </c>
     </row>
   </sheetData>
